--- a/output/topology_excel/8422.xlsx
+++ b/output/topology_excel/8422.xlsx
@@ -425,43 +425,58 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G65"/>
+  <dimension ref="A1:J68"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>房间ID1</t>
+          <t>房间1</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>房间类型1</t>
+          <t>类型1</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>房间ID2</t>
+          <t>面积1</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>房间类型2</t>
+          <t>房间2</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
+          <t>类型2</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>面积2</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
           <t>连接类型</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>连接数量</t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>连接面积</t>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>数量</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>length</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>width</t>
         </is>
       </c>
     </row>
@@ -475,52 +490,70 @@
         </is>
       </c>
       <c r="C2" t="n">
+        <v>143869</v>
+      </c>
+      <c r="D2" t="n">
         <v>3</v>
       </c>
-      <c r="D2" t="inlineStr">
+      <c r="E2" t="inlineStr">
         <is>
           <t>Other</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>门/窗</t>
-        </is>
-      </c>
       <c r="F2" t="n">
-        <v>1</v>
-      </c>
-      <c r="G2" t="n">
-        <v>1700</v>
+        <v>32412</v>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>窗</t>
+        </is>
+      </c>
+      <c r="H2" t="n">
+        <v>1</v>
+      </c>
+      <c r="I2" t="n">
+        <v>68</v>
+      </c>
+      <c r="J2" t="n">
+        <v>25</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Kitchen</t>
+          <t>Living Room</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>3</v>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>Other</t>
-        </is>
+        <v>234855</v>
+      </c>
+      <c r="D3" t="n">
+        <v>7</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>墙</t>
+          <t>Bath</t>
         </is>
       </c>
       <c r="F3" t="n">
-        <v>219</v>
-      </c>
-      <c r="G3" t="n">
-        <v>5475</v>
+        <v>11172</v>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>窗</t>
+        </is>
+      </c>
+      <c r="H3" t="n">
+        <v>1</v>
+      </c>
+      <c r="I3" t="n">
+        <v>73</v>
+      </c>
+      <c r="J3" t="n">
+        <v>17</v>
       </c>
     </row>
     <row r="4">
@@ -533,86 +566,113 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>7</v>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>Bath</t>
-        </is>
+        <v>234855</v>
+      </c>
+      <c r="D4" t="n">
+        <v>6</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>门/窗</t>
+          <t>Hallway</t>
         </is>
       </c>
       <c r="F4" t="n">
-        <v>1</v>
-      </c>
-      <c r="G4" t="n">
-        <v>1241</v>
+        <v>15768</v>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>窗</t>
+        </is>
+      </c>
+      <c r="H4" t="n">
+        <v>1</v>
+      </c>
+      <c r="I4" t="n">
+        <v>89</v>
+      </c>
+      <c r="J4" t="n">
+        <v>17</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Living Room</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>7</v>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>Bath</t>
-        </is>
+        <v>30488</v>
+      </c>
+      <c r="D5" t="n">
+        <v>8</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>墙</t>
+          <t>Hallway</t>
         </is>
       </c>
       <c r="F5" t="n">
-        <v>212</v>
-      </c>
-      <c r="G5" t="n">
-        <v>3604</v>
+        <v>54021</v>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>窗</t>
+        </is>
+      </c>
+      <c r="H5" t="n">
+        <v>1</v>
+      </c>
+      <c r="I5" t="n">
+        <v>69</v>
+      </c>
+      <c r="J5" t="n">
+        <v>25</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Living Room</t>
+          <t>Kitchen</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>6</v>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>Hallway</t>
-        </is>
+        <v>143869</v>
+      </c>
+      <c r="D6" t="n">
+        <v>4</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>门/窗</t>
+          <t>Living Room</t>
         </is>
       </c>
       <c r="F6" t="n">
-        <v>1</v>
-      </c>
-      <c r="G6" t="n">
-        <v>1513</v>
+        <v>313405</v>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>窗</t>
+        </is>
+      </c>
+      <c r="H6" t="n">
+        <v>1</v>
+      </c>
+      <c r="I6" t="n">
+        <v>95</v>
+      </c>
+      <c r="J6" t="n">
+        <v>16</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
@@ -620,110 +680,146 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>6</v>
-      </c>
-      <c r="D7" t="inlineStr">
+        <v>313405</v>
+      </c>
+      <c r="D7" t="n">
+        <v>8</v>
+      </c>
+      <c r="E7" t="inlineStr">
         <is>
           <t>Hallway</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>墙</t>
-        </is>
-      </c>
       <c r="F7" t="n">
-        <v>108</v>
-      </c>
-      <c r="G7" t="n">
-        <v>1836</v>
+        <v>54021</v>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>窗</t>
+        </is>
+      </c>
+      <c r="H7" t="n">
+        <v>1</v>
+      </c>
+      <c r="I7" t="n">
+        <v>78</v>
+      </c>
+      <c r="J7" t="n">
+        <v>21</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Living Room</t>
         </is>
       </c>
       <c r="C8" t="n">
+        <v>234855</v>
+      </c>
+      <c r="D8" t="n">
         <v>8</v>
       </c>
-      <c r="D8" t="inlineStr">
+      <c r="E8" t="inlineStr">
         <is>
           <t>Hallway</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>门/窗</t>
-        </is>
-      </c>
       <c r="F8" t="n">
-        <v>1</v>
-      </c>
-      <c r="G8" t="n">
-        <v>1725</v>
+        <v>54021</v>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>窗</t>
+        </is>
+      </c>
+      <c r="H8" t="n">
+        <v>1</v>
+      </c>
+      <c r="I8" t="n">
+        <v>79</v>
+      </c>
+      <c r="J8" t="n">
+        <v>17</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Kitchen</t>
+          <t>Living Room</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>4</v>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>Living Room</t>
-        </is>
+        <v>313405</v>
+      </c>
+      <c r="D9" t="n">
+        <v>11</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>门/窗</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="F9" t="n">
-        <v>1</v>
-      </c>
-      <c r="G9" t="n">
-        <v>1520</v>
+        <v>37682</v>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>窗</t>
+        </is>
+      </c>
+      <c r="H9" t="n">
+        <v>1</v>
+      </c>
+      <c r="I9" t="n">
+        <v>92</v>
+      </c>
+      <c r="J9" t="n">
+        <v>18</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B10" t="inlineStr">
         <is>
+          <t>Living Room</t>
+        </is>
+      </c>
+      <c r="C10" t="n">
+        <v>234855</v>
+      </c>
+      <c r="D10" t="n">
+        <v>9</v>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
           <t>Kitchen</t>
         </is>
       </c>
-      <c r="C10" t="n">
-        <v>4</v>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>Living Room</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>墙</t>
-        </is>
-      </c>
       <c r="F10" t="n">
-        <v>617</v>
-      </c>
-      <c r="G10" t="n">
-        <v>9872</v>
+        <v>59944</v>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>窗</t>
+        </is>
+      </c>
+      <c r="H10" t="n">
+        <v>1</v>
+      </c>
+      <c r="I10" t="n">
+        <v>67</v>
+      </c>
+      <c r="J10" t="n">
+        <v>17</v>
       </c>
     </row>
     <row r="11">
@@ -736,57 +832,75 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>8</v>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>Hallway</t>
-        </is>
+        <v>313405</v>
+      </c>
+      <c r="D11" t="n">
+        <v>12</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>门/窗</t>
+          <t>Storage</t>
         </is>
       </c>
       <c r="F11" t="n">
-        <v>1</v>
-      </c>
-      <c r="G11" t="n">
-        <v>1638</v>
+        <v>14732</v>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>窗</t>
+        </is>
+      </c>
+      <c r="H11" t="n">
+        <v>1</v>
+      </c>
+      <c r="I11" t="n">
+        <v>59</v>
+      </c>
+      <c r="J11" t="n">
+        <v>15</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Living Room</t>
+          <t>Hallway</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>8</v>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>Hallway</t>
-        </is>
+        <v>54021</v>
+      </c>
+      <c r="D12" t="n">
+        <v>13</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>墙</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="F12" t="n">
-        <v>102</v>
-      </c>
-      <c r="G12" t="n">
-        <v>8064</v>
+        <v>21024</v>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>窗</t>
+        </is>
+      </c>
+      <c r="H12" t="n">
+        <v>1</v>
+      </c>
+      <c r="I12" t="n">
+        <v>80</v>
+      </c>
+      <c r="J12" t="n">
+        <v>21</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="B13" t="inlineStr">
         <is>
@@ -794,23 +908,32 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>8</v>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>Hallway</t>
-        </is>
+        <v>313405</v>
+      </c>
+      <c r="D13" t="n">
+        <v>10</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>门/窗</t>
+          <t>Bedroom</t>
         </is>
       </c>
       <c r="F13" t="n">
-        <v>1</v>
-      </c>
-      <c r="G13" t="n">
-        <v>1343</v>
+        <v>91155</v>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>窗</t>
+        </is>
+      </c>
+      <c r="H13" t="n">
+        <v>1</v>
+      </c>
+      <c r="I13" t="n">
+        <v>78</v>
+      </c>
+      <c r="J13" t="n">
+        <v>13</v>
       </c>
     </row>
     <row r="14">
@@ -823,23 +946,32 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>8</v>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>Hallway</t>
-        </is>
+        <v>234855</v>
+      </c>
+      <c r="D14" t="n">
+        <v>16</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>墙</t>
+          <t>Bedroom</t>
         </is>
       </c>
       <c r="F14" t="n">
-        <v>175</v>
-      </c>
-      <c r="G14" t="n">
-        <v>2975</v>
+        <v>141052</v>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>窗</t>
+        </is>
+      </c>
+      <c r="H14" t="n">
+        <v>1</v>
+      </c>
+      <c r="I14" t="n">
+        <v>81</v>
+      </c>
+      <c r="J14" t="n">
+        <v>17</v>
       </c>
     </row>
     <row r="15">
@@ -852,23 +984,32 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>11</v>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>Other</t>
-        </is>
+        <v>313405</v>
+      </c>
+      <c r="D15" t="n">
+        <v>15</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>门/窗</t>
+          <t>Bath</t>
         </is>
       </c>
       <c r="F15" t="n">
-        <v>1</v>
-      </c>
-      <c r="G15" t="n">
-        <v>1656</v>
+        <v>14097</v>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>窗</t>
+        </is>
+      </c>
+      <c r="H15" t="n">
+        <v>1</v>
+      </c>
+      <c r="I15" t="n">
+        <v>57</v>
+      </c>
+      <c r="J15" t="n">
+        <v>15</v>
       </c>
     </row>
     <row r="16">
@@ -881,28 +1022,37 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>11</v>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>Other</t>
-        </is>
+        <v>313405</v>
+      </c>
+      <c r="D16" t="n">
+        <v>17</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>墙</t>
+          <t>Bedroom</t>
         </is>
       </c>
       <c r="F16" t="n">
-        <v>179</v>
-      </c>
-      <c r="G16" t="n">
-        <v>5107</v>
+        <v>91773</v>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>窗</t>
+        </is>
+      </c>
+      <c r="H16" t="n">
+        <v>1</v>
+      </c>
+      <c r="I16" t="n">
+        <v>79</v>
+      </c>
+      <c r="J16" t="n">
+        <v>13</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="B17" t="inlineStr">
         <is>
@@ -910,81 +1060,108 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>9</v>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>Kitchen</t>
-        </is>
+        <v>313405</v>
+      </c>
+      <c r="D17" t="n">
+        <v>18</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>门/窗</t>
+          <t>Bedroom</t>
         </is>
       </c>
       <c r="F17" t="n">
-        <v>1</v>
-      </c>
-      <c r="G17" t="n">
-        <v>1139</v>
+        <v>87188</v>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>窗</t>
+        </is>
+      </c>
+      <c r="H17" t="n">
+        <v>1</v>
+      </c>
+      <c r="I17" t="n">
+        <v>80</v>
+      </c>
+      <c r="J17" t="n">
+        <v>15</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>2</v>
+        <v>13</v>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Living Room</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>9</v>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>Kitchen</t>
-        </is>
+        <v>21024</v>
+      </c>
+      <c r="D18" t="n">
+        <v>19</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>墙</t>
+          <t>Bath</t>
         </is>
       </c>
       <c r="F18" t="n">
-        <v>146</v>
-      </c>
-      <c r="G18" t="n">
-        <v>5253</v>
+        <v>69960</v>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>窗</t>
+        </is>
+      </c>
+      <c r="H18" t="n">
+        <v>1</v>
+      </c>
+      <c r="I18" t="n">
+        <v>69</v>
+      </c>
+      <c r="J18" t="n">
+        <v>16</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>4</v>
+        <v>14</v>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Living Room</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>12</v>
-      </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>Storage</t>
-        </is>
+        <v>47304</v>
+      </c>
+      <c r="D19" t="n">
+        <v>19</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>门/窗</t>
+          <t>Bath</t>
         </is>
       </c>
       <c r="F19" t="n">
-        <v>1</v>
-      </c>
-      <c r="G19" t="n">
-        <v>885</v>
+        <v>69960</v>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>窗</t>
+        </is>
+      </c>
+      <c r="H19" t="n">
+        <v>1</v>
+      </c>
+      <c r="I19" t="n">
+        <v>73</v>
+      </c>
+      <c r="J19" t="n">
+        <v>16</v>
       </c>
     </row>
     <row r="20">
@@ -997,173 +1174,227 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>12</v>
-      </c>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t>Storage</t>
-        </is>
+        <v>313405</v>
+      </c>
+      <c r="D20" t="n">
+        <v>20</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>墙</t>
+          <t>Hallway</t>
         </is>
       </c>
       <c r="F20" t="n">
-        <v>243</v>
-      </c>
-      <c r="G20" t="n">
-        <v>4026</v>
+        <v>11473</v>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>窗</t>
+        </is>
+      </c>
+      <c r="H20" t="n">
+        <v>1</v>
+      </c>
+      <c r="I20" t="n">
+        <v>94</v>
+      </c>
+      <c r="J20" t="n">
+        <v>17</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Hallway</t>
+          <t>Kitchen</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>13</v>
-      </c>
-      <c r="D21" t="inlineStr">
+        <v>143869</v>
+      </c>
+      <c r="D21" t="n">
+        <v>3</v>
+      </c>
+      <c r="E21" t="inlineStr">
         <is>
           <t>Other</t>
         </is>
       </c>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>门/窗</t>
-        </is>
-      </c>
       <c r="F21" t="n">
-        <v>1</v>
-      </c>
-      <c r="G21" t="n">
-        <v>1680</v>
+        <v>32412</v>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>墙</t>
+        </is>
+      </c>
+      <c r="H21" t="n">
+        <v>1</v>
+      </c>
+      <c r="I21" t="n">
+        <v>219</v>
+      </c>
+      <c r="J21" t="n">
+        <v>25</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
+        <v>1</v>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Kitchen</t>
+        </is>
+      </c>
+      <c r="C22" t="n">
+        <v>143869</v>
+      </c>
+      <c r="D22" t="n">
         <v>4</v>
       </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>Living Room</t>
-        </is>
-      </c>
-      <c r="C22" t="n">
-        <v>10</v>
-      </c>
-      <c r="D22" t="inlineStr">
-        <is>
-          <t>Bedroom</t>
-        </is>
-      </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>门/窗</t>
+          <t>Living Room</t>
         </is>
       </c>
       <c r="F22" t="n">
-        <v>1</v>
-      </c>
-      <c r="G22" t="n">
-        <v>1014</v>
+        <v>313405</v>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>墙</t>
+        </is>
+      </c>
+      <c r="H22" t="n">
+        <v>1</v>
+      </c>
+      <c r="I22" t="n">
+        <v>376</v>
+      </c>
+      <c r="J22" t="n">
+        <v>273</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Living Room</t>
+          <t>Kitchen</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>10</v>
-      </c>
-      <c r="D23" t="inlineStr">
-        <is>
-          <t>Bedroom</t>
-        </is>
+        <v>143869</v>
+      </c>
+      <c r="D23" t="n">
+        <v>2</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>墙</t>
+          <t>Living Room</t>
         </is>
       </c>
       <c r="F23" t="n">
-        <v>604</v>
-      </c>
-      <c r="G23" t="n">
-        <v>8779</v>
+        <v>234855</v>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>墙</t>
+        </is>
+      </c>
+      <c r="H23" t="n">
+        <v>1</v>
+      </c>
+      <c r="I23" t="n">
+        <v>200</v>
+      </c>
+      <c r="J23" t="n">
+        <v>17</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Living Room</t>
+          <t>Kitchen</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>16</v>
-      </c>
-      <c r="D24" t="inlineStr">
-        <is>
-          <t>Bedroom</t>
-        </is>
+        <v>143869</v>
+      </c>
+      <c r="D24" t="n">
+        <v>5</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>门/窗</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="F24" t="n">
-        <v>1</v>
-      </c>
-      <c r="G24" t="n">
-        <v>1377</v>
+        <v>30488</v>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>墙</t>
+        </is>
+      </c>
+      <c r="H24" t="n">
+        <v>1</v>
+      </c>
+      <c r="I24" t="n">
+        <v>206</v>
+      </c>
+      <c r="J24" t="n">
+        <v>25</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Living Room</t>
+          <t>Kitchen</t>
         </is>
       </c>
       <c r="C25" t="n">
-        <v>16</v>
-      </c>
-      <c r="D25" t="inlineStr">
-        <is>
-          <t>Bedroom</t>
-        </is>
+        <v>143869</v>
+      </c>
+      <c r="D25" t="n">
+        <v>8</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>墙</t>
+          <t>Hallway</t>
         </is>
       </c>
       <c r="F25" t="n">
-        <v>140</v>
-      </c>
-      <c r="G25" t="n">
-        <v>6681</v>
+        <v>54021</v>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>墙</t>
+        </is>
+      </c>
+      <c r="H25" t="n">
+        <v>1</v>
+      </c>
+      <c r="I25" t="n">
+        <v>41</v>
+      </c>
+      <c r="J25" t="n">
+        <v>25</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="B26" t="inlineStr">
         <is>
@@ -1171,28 +1402,37 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>15</v>
-      </c>
-      <c r="D26" t="inlineStr">
-        <is>
-          <t>Bath</t>
-        </is>
+        <v>234855</v>
+      </c>
+      <c r="D26" t="n">
+        <v>3</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>门/窗</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="F26" t="n">
-        <v>1</v>
-      </c>
-      <c r="G26" t="n">
-        <v>855</v>
+        <v>32412</v>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>墙</t>
+        </is>
+      </c>
+      <c r="H26" t="n">
+        <v>1</v>
+      </c>
+      <c r="I26" t="n">
+        <v>219</v>
+      </c>
+      <c r="J26" t="n">
+        <v>27</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="B27" t="inlineStr">
         <is>
@@ -1200,28 +1440,37 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>15</v>
-      </c>
-      <c r="D27" t="inlineStr">
-        <is>
-          <t>Bath</t>
-        </is>
+        <v>234855</v>
+      </c>
+      <c r="D27" t="n">
+        <v>5</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>墙</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="F27" t="n">
-        <v>111</v>
-      </c>
-      <c r="G27" t="n">
-        <v>1665</v>
+        <v>30488</v>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>墙</t>
+        </is>
+      </c>
+      <c r="H27" t="n">
+        <v>1</v>
+      </c>
+      <c r="I27" t="n">
+        <v>142</v>
+      </c>
+      <c r="J27" t="n">
+        <v>100</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="B28" t="inlineStr">
         <is>
@@ -1229,28 +1478,37 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>17</v>
-      </c>
-      <c r="D28" t="inlineStr">
-        <is>
-          <t>Bedroom</t>
-        </is>
+        <v>234855</v>
+      </c>
+      <c r="D28" t="n">
+        <v>6</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>门/窗</t>
+          <t>Hallway</t>
         </is>
       </c>
       <c r="F28" t="n">
-        <v>1</v>
-      </c>
-      <c r="G28" t="n">
-        <v>1027</v>
+        <v>15768</v>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>墙</t>
+        </is>
+      </c>
+      <c r="H28" t="n">
+        <v>1</v>
+      </c>
+      <c r="I28" t="n">
+        <v>163</v>
+      </c>
+      <c r="J28" t="n">
+        <v>125</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="B29" t="inlineStr">
         <is>
@@ -1258,28 +1516,37 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>17</v>
-      </c>
-      <c r="D29" t="inlineStr">
-        <is>
-          <t>Bedroom</t>
-        </is>
+        <v>234855</v>
+      </c>
+      <c r="D29" t="n">
+        <v>9</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>墙</t>
+          <t>Kitchen</t>
         </is>
       </c>
       <c r="F29" t="n">
-        <v>159</v>
-      </c>
-      <c r="G29" t="n">
-        <v>2067</v>
+        <v>59944</v>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>墙</t>
+        </is>
+      </c>
+      <c r="H29" t="n">
+        <v>1</v>
+      </c>
+      <c r="I29" t="n">
+        <v>416</v>
+      </c>
+      <c r="J29" t="n">
+        <v>163</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="B30" t="inlineStr">
         <is>
@@ -1287,28 +1554,37 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>18</v>
-      </c>
-      <c r="D30" t="inlineStr">
-        <is>
-          <t>Bedroom</t>
-        </is>
+        <v>234855</v>
+      </c>
+      <c r="D30" t="n">
+        <v>7</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>门/窗</t>
+          <t>Bath</t>
         </is>
       </c>
       <c r="F30" t="n">
-        <v>1</v>
-      </c>
-      <c r="G30" t="n">
-        <v>1200</v>
+        <v>11172</v>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>墙</t>
+        </is>
+      </c>
+      <c r="H30" t="n">
+        <v>1</v>
+      </c>
+      <c r="I30" t="n">
+        <v>131</v>
+      </c>
+      <c r="J30" t="n">
+        <v>115</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="B31" t="inlineStr">
         <is>
@@ -1316,86 +1592,113 @@
         </is>
       </c>
       <c r="C31" t="n">
-        <v>18</v>
-      </c>
-      <c r="D31" t="inlineStr">
-        <is>
-          <t>Bedroom</t>
-        </is>
+        <v>234855</v>
+      </c>
+      <c r="D31" t="n">
+        <v>8</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>墙</t>
+          <t>Hallway</t>
         </is>
       </c>
       <c r="F31" t="n">
-        <v>167</v>
-      </c>
-      <c r="G31" t="n">
-        <v>7965</v>
+        <v>54021</v>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>墙</t>
+        </is>
+      </c>
+      <c r="H31" t="n">
+        <v>1</v>
+      </c>
+      <c r="I31" t="n">
+        <v>175</v>
+      </c>
+      <c r="J31" t="n">
+        <v>17</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
+        <v>2</v>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Living Room</t>
+        </is>
+      </c>
+      <c r="C32" t="n">
+        <v>234855</v>
+      </c>
+      <c r="D32" t="n">
         <v>13</v>
       </c>
-      <c r="B32" t="inlineStr">
+      <c r="E32" t="inlineStr">
         <is>
           <t>Other</t>
         </is>
       </c>
-      <c r="C32" t="n">
-        <v>19</v>
-      </c>
-      <c r="D32" t="inlineStr">
-        <is>
-          <t>Bath</t>
-        </is>
-      </c>
-      <c r="E32" t="inlineStr">
-        <is>
-          <t>门/窗</t>
-        </is>
-      </c>
       <c r="F32" t="n">
-        <v>1</v>
-      </c>
-      <c r="G32" t="n">
-        <v>1104</v>
+        <v>21024</v>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>墙</t>
+        </is>
+      </c>
+      <c r="H32" t="n">
+        <v>1</v>
+      </c>
+      <c r="I32" t="n">
+        <v>72</v>
+      </c>
+      <c r="J32" t="n">
+        <v>26</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>13</v>
+        <v>2</v>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Living Room</t>
         </is>
       </c>
       <c r="C33" t="n">
-        <v>19</v>
-      </c>
-      <c r="D33" t="inlineStr">
-        <is>
-          <t>Bath</t>
-        </is>
+        <v>234855</v>
+      </c>
+      <c r="D33" t="n">
+        <v>16</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>墙</t>
+          <t>Bedroom</t>
         </is>
       </c>
       <c r="F33" t="n">
-        <v>96</v>
-      </c>
-      <c r="G33" t="n">
-        <v>1536</v>
+        <v>141052</v>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>墙</t>
+        </is>
+      </c>
+      <c r="H33" t="n">
+        <v>1</v>
+      </c>
+      <c r="I33" t="n">
+        <v>123</v>
+      </c>
+      <c r="J33" t="n">
+        <v>17</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>14</v>
+        <v>3</v>
       </c>
       <c r="B34" t="inlineStr">
         <is>
@@ -1403,52 +1706,70 @@
         </is>
       </c>
       <c r="C34" t="n">
-        <v>19</v>
-      </c>
-      <c r="D34" t="inlineStr">
-        <is>
-          <t>Bath</t>
-        </is>
+        <v>32412</v>
+      </c>
+      <c r="D34" t="n">
+        <v>5</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>门/窗</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="F34" t="n">
-        <v>1</v>
-      </c>
-      <c r="G34" t="n">
-        <v>1168</v>
+        <v>30488</v>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>墙</t>
+        </is>
+      </c>
+      <c r="H34" t="n">
+        <v>1</v>
+      </c>
+      <c r="I34" t="n">
+        <v>148</v>
+      </c>
+      <c r="J34" t="n">
+        <v>17</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Living Room</t>
         </is>
       </c>
       <c r="C35" t="n">
-        <v>19</v>
-      </c>
-      <c r="D35" t="inlineStr">
-        <is>
-          <t>Bath</t>
-        </is>
+        <v>313405</v>
+      </c>
+      <c r="D35" t="n">
+        <v>8</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>墙</t>
+          <t>Hallway</t>
         </is>
       </c>
       <c r="F35" t="n">
-        <v>216</v>
-      </c>
-      <c r="G35" t="n">
-        <v>3456</v>
+        <v>54021</v>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>墙</t>
+        </is>
+      </c>
+      <c r="H35" t="n">
+        <v>1</v>
+      </c>
+      <c r="I35" t="n">
+        <v>84</v>
+      </c>
+      <c r="J35" t="n">
+        <v>21</v>
       </c>
     </row>
     <row r="36">
@@ -1461,23 +1782,32 @@
         </is>
       </c>
       <c r="C36" t="n">
-        <v>20</v>
-      </c>
-      <c r="D36" t="inlineStr">
-        <is>
-          <t>Hallway</t>
-        </is>
+        <v>313405</v>
+      </c>
+      <c r="D36" t="n">
+        <v>10</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>门/窗</t>
+          <t>Bedroom</t>
         </is>
       </c>
       <c r="F36" t="n">
-        <v>1</v>
-      </c>
-      <c r="G36" t="n">
-        <v>1598</v>
+        <v>91155</v>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>墙</t>
+        </is>
+      </c>
+      <c r="H36" t="n">
+        <v>1</v>
+      </c>
+      <c r="I36" t="n">
+        <v>322</v>
+      </c>
+      <c r="J36" t="n">
+        <v>311</v>
       </c>
     </row>
     <row r="37">
@@ -1490,115 +1820,151 @@
         </is>
       </c>
       <c r="C37" t="n">
-        <v>20</v>
-      </c>
-      <c r="D37" t="inlineStr">
-        <is>
-          <t>Hallway</t>
-        </is>
+        <v>313405</v>
+      </c>
+      <c r="D37" t="n">
+        <v>11</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>墙</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="F37" t="n">
-        <v>149</v>
-      </c>
-      <c r="G37" t="n">
-        <v>2533</v>
+        <v>37682</v>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>墙</t>
+        </is>
+      </c>
+      <c r="H37" t="n">
+        <v>1</v>
+      </c>
+      <c r="I37" t="n">
+        <v>329</v>
+      </c>
+      <c r="J37" t="n">
+        <v>147</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Kitchen</t>
+          <t>Living Room</t>
         </is>
       </c>
       <c r="C38" t="n">
-        <v>2</v>
-      </c>
-      <c r="D38" t="inlineStr">
-        <is>
-          <t>Living Room</t>
-        </is>
+        <v>313405</v>
+      </c>
+      <c r="D38" t="n">
+        <v>12</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>墙</t>
+          <t>Storage</t>
         </is>
       </c>
       <c r="F38" t="n">
-        <v>17</v>
-      </c>
-      <c r="G38" t="n">
-        <v>3400</v>
+        <v>14732</v>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>墙</t>
+        </is>
+      </c>
+      <c r="H38" t="n">
+        <v>1</v>
+      </c>
+      <c r="I38" t="n">
+        <v>142</v>
+      </c>
+      <c r="J38" t="n">
+        <v>134</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Kitchen</t>
+          <t>Living Room</t>
         </is>
       </c>
       <c r="C39" t="n">
-        <v>5</v>
-      </c>
-      <c r="D39" t="inlineStr">
-        <is>
-          <t>Other</t>
-        </is>
+        <v>313405</v>
+      </c>
+      <c r="D39" t="n">
+        <v>15</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>墙</t>
+          <t>Bath</t>
         </is>
       </c>
       <c r="F39" t="n">
-        <v>206</v>
-      </c>
-      <c r="G39" t="n">
-        <v>5150</v>
+        <v>14097</v>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>墙</t>
+        </is>
+      </c>
+      <c r="H39" t="n">
+        <v>1</v>
+      </c>
+      <c r="I39" t="n">
+        <v>111</v>
+      </c>
+      <c r="J39" t="n">
+        <v>15</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Kitchen</t>
+          <t>Living Room</t>
         </is>
       </c>
       <c r="C40" t="n">
-        <v>8</v>
-      </c>
-      <c r="D40" t="inlineStr">
-        <is>
-          <t>Hallway</t>
-        </is>
+        <v>313405</v>
+      </c>
+      <c r="D40" t="n">
+        <v>17</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>墙</t>
+          <t>Bedroom</t>
         </is>
       </c>
       <c r="F40" t="n">
-        <v>41</v>
-      </c>
-      <c r="G40" t="n">
-        <v>1025</v>
+        <v>91773</v>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>墙</t>
+        </is>
+      </c>
+      <c r="H40" t="n">
+        <v>1</v>
+      </c>
+      <c r="I40" t="n">
+        <v>159</v>
+      </c>
+      <c r="J40" t="n">
+        <v>13</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="B41" t="inlineStr">
         <is>
@@ -1606,28 +1972,37 @@
         </is>
       </c>
       <c r="C41" t="n">
-        <v>3</v>
-      </c>
-      <c r="D41" t="inlineStr">
-        <is>
-          <t>Other</t>
-        </is>
+        <v>313405</v>
+      </c>
+      <c r="D41" t="n">
+        <v>18</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>墙</t>
+          <t>Bedroom</t>
         </is>
       </c>
       <c r="F41" t="n">
-        <v>219</v>
-      </c>
-      <c r="G41" t="n">
-        <v>5913</v>
+        <v>87188</v>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>墙</t>
+        </is>
+      </c>
+      <c r="H41" t="n">
+        <v>1</v>
+      </c>
+      <c r="I41" t="n">
+        <v>146</v>
+      </c>
+      <c r="J41" t="n">
+        <v>15</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="B42" t="inlineStr">
         <is>
@@ -1635,202 +2010,265 @@
         </is>
       </c>
       <c r="C42" t="n">
-        <v>5</v>
-      </c>
-      <c r="D42" t="inlineStr">
-        <is>
-          <t>Other</t>
-        </is>
+        <v>313405</v>
+      </c>
+      <c r="D42" t="n">
+        <v>20</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>墙</t>
+          <t>Hallway</t>
         </is>
       </c>
       <c r="F42" t="n">
-        <v>100</v>
-      </c>
-      <c r="G42" t="n">
-        <v>4655</v>
+        <v>11473</v>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>墙</t>
+        </is>
+      </c>
+      <c r="H42" t="n">
+        <v>1</v>
+      </c>
+      <c r="I42" t="n">
+        <v>149</v>
+      </c>
+      <c r="J42" t="n">
+        <v>17</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Living Room</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="C43" t="n">
-        <v>4</v>
-      </c>
-      <c r="D43" t="inlineStr">
-        <is>
-          <t>Living Room</t>
-        </is>
+        <v>30488</v>
+      </c>
+      <c r="D43" t="n">
+        <v>7</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>墙</t>
+          <t>Bath</t>
         </is>
       </c>
       <c r="F43" t="n">
-        <v>17</v>
-      </c>
-      <c r="G43" t="n">
-        <v>8593</v>
+        <v>11172</v>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>墙</t>
+        </is>
+      </c>
+      <c r="H43" t="n">
+        <v>1</v>
+      </c>
+      <c r="I43" t="n">
+        <v>106</v>
+      </c>
+      <c r="J43" t="n">
+        <v>27</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Living Room</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="C44" t="n">
-        <v>11</v>
-      </c>
-      <c r="D44" t="inlineStr">
-        <is>
-          <t>Other</t>
-        </is>
+        <v>30488</v>
+      </c>
+      <c r="D44" t="n">
+        <v>8</v>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>墙</t>
+          <t>Hallway</t>
         </is>
       </c>
       <c r="F44" t="n">
-        <v>21</v>
-      </c>
-      <c r="G44" t="n">
-        <v>7917</v>
+        <v>54021</v>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>墙</t>
+        </is>
+      </c>
+      <c r="H44" t="n">
+        <v>1</v>
+      </c>
+      <c r="I44" t="n">
+        <v>148</v>
+      </c>
+      <c r="J44" t="n">
+        <v>25</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Living Room</t>
+          <t>Hallway</t>
         </is>
       </c>
       <c r="C45" t="n">
-        <v>13</v>
-      </c>
-      <c r="D45" t="inlineStr">
-        <is>
-          <t>Other</t>
-        </is>
+        <v>15768</v>
+      </c>
+      <c r="D45" t="n">
+        <v>9</v>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>墙</t>
+          <t>Kitchen</t>
         </is>
       </c>
       <c r="F45" t="n">
-        <v>72</v>
-      </c>
-      <c r="G45" t="n">
-        <v>1872</v>
+        <v>59944</v>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>墙</t>
+        </is>
+      </c>
+      <c r="H45" t="n">
+        <v>1</v>
+      </c>
+      <c r="I45" t="n">
+        <v>108</v>
+      </c>
+      <c r="J45" t="n">
+        <v>17</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Living Room</t>
+          <t>Bath</t>
         </is>
       </c>
       <c r="C46" t="n">
-        <v>7</v>
-      </c>
-      <c r="D46" t="inlineStr">
-        <is>
-          <t>Bath</t>
-        </is>
+        <v>11172</v>
+      </c>
+      <c r="D46" t="n">
+        <v>8</v>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>墙</t>
+          <t>Hallway</t>
         </is>
       </c>
       <c r="F46" t="n">
-        <v>8</v>
-      </c>
-      <c r="G46" t="n">
-        <v>4280</v>
+        <v>54021</v>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>墙</t>
+        </is>
+      </c>
+      <c r="H46" t="n">
+        <v>1</v>
+      </c>
+      <c r="I46" t="n">
+        <v>98</v>
+      </c>
+      <c r="J46" t="n">
+        <v>17</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Living Room</t>
+          <t>Hallway</t>
         </is>
       </c>
       <c r="C47" t="n">
-        <v>14</v>
-      </c>
-      <c r="D47" t="inlineStr">
+        <v>54021</v>
+      </c>
+      <c r="D47" t="n">
+        <v>11</v>
+      </c>
+      <c r="E47" t="inlineStr">
         <is>
           <t>Other</t>
         </is>
       </c>
-      <c r="E47" t="inlineStr">
-        <is>
-          <t>墙</t>
-        </is>
-      </c>
       <c r="F47" t="n">
-        <v>17</v>
-      </c>
-      <c r="G47" t="n">
-        <v>5950</v>
+        <v>37682</v>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>墙</t>
+        </is>
+      </c>
+      <c r="H47" t="n">
+        <v>1</v>
+      </c>
+      <c r="I47" t="n">
+        <v>123</v>
+      </c>
+      <c r="J47" t="n">
+        <v>73</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="B48" t="inlineStr">
         <is>
+          <t>Hallway</t>
+        </is>
+      </c>
+      <c r="C48" t="n">
+        <v>54021</v>
+      </c>
+      <c r="D48" t="n">
+        <v>14</v>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
           <t>Other</t>
         </is>
       </c>
-      <c r="C48" t="n">
-        <v>7</v>
-      </c>
-      <c r="D48" t="inlineStr">
-        <is>
-          <t>Bath</t>
-        </is>
-      </c>
-      <c r="E48" t="inlineStr">
-        <is>
-          <t>墙</t>
-        </is>
-      </c>
       <c r="F48" t="n">
-        <v>106</v>
-      </c>
-      <c r="G48" t="n">
-        <v>2862</v>
+        <v>47304</v>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>墙</t>
+        </is>
+      </c>
+      <c r="H48" t="n">
+        <v>1</v>
+      </c>
+      <c r="I48" t="n">
+        <v>216</v>
+      </c>
+      <c r="J48" t="n">
+        <v>73</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="B49" t="inlineStr">
         <is>
@@ -1838,139 +2276,184 @@
         </is>
       </c>
       <c r="C49" t="n">
-        <v>9</v>
-      </c>
-      <c r="D49" t="inlineStr">
-        <is>
-          <t>Kitchen</t>
-        </is>
+        <v>54021</v>
+      </c>
+      <c r="D49" t="n">
+        <v>13</v>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>墙</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="F49" t="n">
-        <v>108</v>
-      </c>
-      <c r="G49" t="n">
-        <v>1836</v>
+        <v>21024</v>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>墙</t>
+        </is>
+      </c>
+      <c r="H49" t="n">
+        <v>1</v>
+      </c>
+      <c r="I49" t="n">
+        <v>96</v>
+      </c>
+      <c r="J49" t="n">
+        <v>21</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Hallway</t>
+          <t>Kitchen</t>
         </is>
       </c>
       <c r="C50" t="n">
-        <v>11</v>
-      </c>
-      <c r="D50" t="inlineStr">
-        <is>
-          <t>Other</t>
-        </is>
+        <v>59944</v>
+      </c>
+      <c r="D50" t="n">
+        <v>16</v>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>墙</t>
+          <t>Bedroom</t>
         </is>
       </c>
       <c r="F50" t="n">
-        <v>73</v>
-      </c>
-      <c r="G50" t="n">
-        <v>6837</v>
+        <v>141052</v>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>墙</t>
+        </is>
+      </c>
+      <c r="H50" t="n">
+        <v>1</v>
+      </c>
+      <c r="I50" t="n">
+        <v>254</v>
+      </c>
+      <c r="J50" t="n">
+        <v>17</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Hallway</t>
+          <t>Bedroom</t>
         </is>
       </c>
       <c r="C51" t="n">
-        <v>14</v>
-      </c>
-      <c r="D51" t="inlineStr">
-        <is>
-          <t>Other</t>
-        </is>
+        <v>91155</v>
+      </c>
+      <c r="D51" t="n">
+        <v>17</v>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>墙</t>
+          <t>Bedroom</t>
         </is>
       </c>
       <c r="F51" t="n">
-        <v>102</v>
-      </c>
-      <c r="G51" t="n">
-        <v>7446</v>
+        <v>91773</v>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>墙</t>
+        </is>
+      </c>
+      <c r="H51" t="n">
+        <v>1</v>
+      </c>
+      <c r="I51" t="n">
+        <v>309</v>
+      </c>
+      <c r="J51" t="n">
+        <v>17</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Kitchen</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="C52" t="n">
-        <v>16</v>
-      </c>
-      <c r="D52" t="inlineStr">
-        <is>
-          <t>Bedroom</t>
-        </is>
+        <v>37682</v>
+      </c>
+      <c r="D52" t="n">
+        <v>12</v>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>墙</t>
+          <t>Storage</t>
         </is>
       </c>
       <c r="F52" t="n">
-        <v>254</v>
-      </c>
-      <c r="G52" t="n">
-        <v>4318</v>
+        <v>14732</v>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>墙</t>
+        </is>
+      </c>
+      <c r="H52" t="n">
+        <v>1</v>
+      </c>
+      <c r="I52" t="n">
+        <v>116</v>
+      </c>
+      <c r="J52" t="n">
+        <v>21</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Bedroom</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="C53" t="n">
-        <v>17</v>
-      </c>
-      <c r="D53" t="inlineStr">
-        <is>
-          <t>Bedroom</t>
-        </is>
+        <v>37682</v>
+      </c>
+      <c r="D53" t="n">
+        <v>14</v>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>墙</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="F53" t="n">
-        <v>309</v>
-      </c>
-      <c r="G53" t="n">
-        <v>5253</v>
+        <v>47304</v>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>墙</t>
+        </is>
+      </c>
+      <c r="H53" t="n">
+        <v>1</v>
+      </c>
+      <c r="I53" t="n">
+        <v>133</v>
+      </c>
+      <c r="J53" t="n">
+        <v>21</v>
       </c>
     </row>
     <row r="54">
@@ -1983,23 +2466,32 @@
         </is>
       </c>
       <c r="C54" t="n">
-        <v>14</v>
-      </c>
-      <c r="D54" t="inlineStr">
-        <is>
-          <t>Other</t>
-        </is>
+        <v>37682</v>
+      </c>
+      <c r="D54" t="n">
+        <v>15</v>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>墙</t>
+          <t>Bath</t>
         </is>
       </c>
       <c r="F54" t="n">
-        <v>133</v>
-      </c>
-      <c r="G54" t="n">
-        <v>2793</v>
+        <v>14097</v>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>墙</t>
+        </is>
+      </c>
+      <c r="H54" t="n">
+        <v>1</v>
+      </c>
+      <c r="I54" t="n">
+        <v>98</v>
+      </c>
+      <c r="J54" t="n">
+        <v>21</v>
       </c>
     </row>
     <row r="55">
@@ -2012,52 +2504,70 @@
         </is>
       </c>
       <c r="C55" t="n">
+        <v>37682</v>
+      </c>
+      <c r="D55" t="n">
         <v>18</v>
       </c>
-      <c r="D55" t="inlineStr">
+      <c r="E55" t="inlineStr">
         <is>
           <t>Bedroom</t>
         </is>
       </c>
-      <c r="E55" t="inlineStr">
-        <is>
-          <t>墙</t>
-        </is>
-      </c>
       <c r="F55" t="n">
+        <v>87188</v>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>墙</t>
+        </is>
+      </c>
+      <c r="H55" t="n">
+        <v>1</v>
+      </c>
+      <c r="I55" t="n">
         <v>159</v>
       </c>
-      <c r="G55" t="n">
-        <v>4770</v>
+      <c r="J55" t="n">
+        <v>30</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
+        <v>12</v>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>Storage</t>
+        </is>
+      </c>
+      <c r="C56" t="n">
+        <v>14732</v>
+      </c>
+      <c r="D56" t="n">
+        <v>15</v>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>Bath</t>
+        </is>
+      </c>
+      <c r="F56" t="n">
+        <v>14097</v>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>墙</t>
+        </is>
+      </c>
+      <c r="H56" t="n">
+        <v>1</v>
+      </c>
+      <c r="I56" t="n">
+        <v>127</v>
+      </c>
+      <c r="J56" t="n">
         <v>13</v>
-      </c>
-      <c r="B56" t="inlineStr">
-        <is>
-          <t>Other</t>
-        </is>
-      </c>
-      <c r="C56" t="n">
-        <v>14</v>
-      </c>
-      <c r="D56" t="inlineStr">
-        <is>
-          <t>Other</t>
-        </is>
-      </c>
-      <c r="E56" t="inlineStr">
-        <is>
-          <t>墙</t>
-        </is>
-      </c>
-      <c r="F56" t="n">
-        <v>219</v>
-      </c>
-      <c r="G56" t="n">
-        <v>3942</v>
       </c>
     </row>
     <row r="57">
@@ -2070,28 +2580,37 @@
         </is>
       </c>
       <c r="C57" t="n">
-        <v>16</v>
-      </c>
-      <c r="D57" t="inlineStr">
-        <is>
-          <t>Bedroom</t>
-        </is>
+        <v>21024</v>
+      </c>
+      <c r="D57" t="n">
+        <v>14</v>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>墙</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="F57" t="n">
-        <v>130</v>
-      </c>
-      <c r="G57" t="n">
-        <v>3380</v>
+        <v>47304</v>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>墙</t>
+        </is>
+      </c>
+      <c r="H57" t="n">
+        <v>1</v>
+      </c>
+      <c r="I57" t="n">
+        <v>219</v>
+      </c>
+      <c r="J57" t="n">
+        <v>18</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B58" t="inlineStr">
         <is>
@@ -2099,28 +2618,37 @@
         </is>
       </c>
       <c r="C58" t="n">
-        <v>15</v>
-      </c>
-      <c r="D58" t="inlineStr">
-        <is>
-          <t>Bath</t>
-        </is>
+        <v>21024</v>
+      </c>
+      <c r="D58" t="n">
+        <v>16</v>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>墙</t>
+          <t>Bedroom</t>
         </is>
       </c>
       <c r="F58" t="n">
-        <v>13</v>
-      </c>
-      <c r="G58" t="n">
-        <v>2704</v>
+        <v>141052</v>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>墙</t>
+        </is>
+      </c>
+      <c r="H58" t="n">
+        <v>1</v>
+      </c>
+      <c r="I58" t="n">
+        <v>130</v>
+      </c>
+      <c r="J58" t="n">
+        <v>26</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B59" t="inlineStr">
         <is>
@@ -2128,144 +2656,189 @@
         </is>
       </c>
       <c r="C59" t="n">
-        <v>18</v>
-      </c>
-      <c r="D59" t="inlineStr">
-        <is>
-          <t>Bedroom</t>
-        </is>
+        <v>21024</v>
+      </c>
+      <c r="D59" t="n">
+        <v>19</v>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>墙</t>
+          <t>Bath</t>
         </is>
       </c>
       <c r="F59" t="n">
-        <v>56</v>
-      </c>
-      <c r="G59" t="n">
-        <v>1568</v>
+        <v>69960</v>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>墙</t>
+        </is>
+      </c>
+      <c r="H59" t="n">
+        <v>1</v>
+      </c>
+      <c r="I59" t="n">
+        <v>96</v>
+      </c>
+      <c r="J59" t="n">
+        <v>16</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Bedroom</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="C60" t="n">
-        <v>18</v>
-      </c>
-      <c r="D60" t="inlineStr">
-        <is>
-          <t>Bedroom</t>
-        </is>
+        <v>47304</v>
+      </c>
+      <c r="D60" t="n">
+        <v>15</v>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>墙</t>
+          <t>Bath</t>
         </is>
       </c>
       <c r="F60" t="n">
-        <v>16</v>
-      </c>
-      <c r="G60" t="n">
-        <v>6144</v>
+        <v>14097</v>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>墙</t>
+        </is>
+      </c>
+      <c r="H60" t="n">
+        <v>1</v>
+      </c>
+      <c r="I60" t="n">
+        <v>208</v>
+      </c>
+      <c r="J60" t="n">
+        <v>13</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="B61" t="inlineStr">
         <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="C61" t="n">
+        <v>47304</v>
+      </c>
+      <c r="D61" t="n">
+        <v>18</v>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
           <t>Bedroom</t>
         </is>
       </c>
-      <c r="C61" t="n">
-        <v>19</v>
-      </c>
-      <c r="D61" t="inlineStr">
-        <is>
-          <t>Bath</t>
-        </is>
-      </c>
-      <c r="E61" t="inlineStr">
-        <is>
-          <t>墙</t>
-        </is>
-      </c>
       <c r="F61" t="n">
-        <v>212</v>
-      </c>
-      <c r="G61" t="n">
-        <v>5512</v>
+        <v>87188</v>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>墙</t>
+        </is>
+      </c>
+      <c r="H61" t="n">
+        <v>1</v>
+      </c>
+      <c r="I61" t="n">
+        <v>56</v>
+      </c>
+      <c r="J61" t="n">
+        <v>28</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Bedroom</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="C62" t="n">
-        <v>18</v>
-      </c>
-      <c r="D62" t="inlineStr">
-        <is>
-          <t>Bedroom</t>
-        </is>
+        <v>47304</v>
+      </c>
+      <c r="D62" t="n">
+        <v>19</v>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>墙</t>
+          <t>Bath</t>
         </is>
       </c>
       <c r="F62" t="n">
-        <v>42</v>
-      </c>
-      <c r="G62" t="n">
-        <v>7434</v>
+        <v>69960</v>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>墙</t>
+        </is>
+      </c>
+      <c r="H62" t="n">
+        <v>1</v>
+      </c>
+      <c r="I62" t="n">
+        <v>216</v>
+      </c>
+      <c r="J62" t="n">
+        <v>16</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
+        <v>15</v>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>Bath</t>
+        </is>
+      </c>
+      <c r="C63" t="n">
+        <v>14097</v>
+      </c>
+      <c r="D63" t="n">
+        <v>18</v>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>Bedroom</t>
+        </is>
+      </c>
+      <c r="F63" t="n">
+        <v>87188</v>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>墙</t>
+        </is>
+      </c>
+      <c r="H63" t="n">
+        <v>1</v>
+      </c>
+      <c r="I63" t="n">
+        <v>127</v>
+      </c>
+      <c r="J63" t="n">
         <v>17</v>
-      </c>
-      <c r="B63" t="inlineStr">
-        <is>
-          <t>Bedroom</t>
-        </is>
-      </c>
-      <c r="C63" t="n">
-        <v>20</v>
-      </c>
-      <c r="D63" t="inlineStr">
-        <is>
-          <t>Hallway</t>
-        </is>
-      </c>
-      <c r="E63" t="inlineStr">
-        <is>
-          <t>墙</t>
-        </is>
-      </c>
-      <c r="F63" t="n">
-        <v>77</v>
-      </c>
-      <c r="G63" t="n">
-        <v>1001</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="B64" t="inlineStr">
         <is>
@@ -2273,52 +2846,184 @@
         </is>
       </c>
       <c r="C64" t="n">
+        <v>141052</v>
+      </c>
+      <c r="D64" t="n">
         <v>19</v>
       </c>
-      <c r="D64" t="inlineStr">
+      <c r="E64" t="inlineStr">
         <is>
           <t>Bath</t>
         </is>
       </c>
-      <c r="E64" t="inlineStr">
-        <is>
-          <t>墙</t>
-        </is>
-      </c>
       <c r="F64" t="n">
+        <v>69960</v>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>墙</t>
+        </is>
+      </c>
+      <c r="H64" t="n">
+        <v>1</v>
+      </c>
+      <c r="I64" t="n">
         <v>212</v>
       </c>
-      <c r="G64" t="n">
-        <v>5936</v>
+      <c r="J64" t="n">
+        <v>26</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
+        <v>17</v>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>Bedroom</t>
+        </is>
+      </c>
+      <c r="C65" t="n">
+        <v>91773</v>
+      </c>
+      <c r="D65" t="n">
         <v>18</v>
       </c>
-      <c r="B65" t="inlineStr">
+      <c r="E65" t="inlineStr">
         <is>
           <t>Bedroom</t>
         </is>
       </c>
-      <c r="C65" t="n">
+      <c r="F65" t="n">
+        <v>87188</v>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>墙</t>
+        </is>
+      </c>
+      <c r="H65" t="n">
+        <v>1</v>
+      </c>
+      <c r="I65" t="n">
+        <v>177</v>
+      </c>
+      <c r="J65" t="n">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="n">
+        <v>17</v>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>Bedroom</t>
+        </is>
+      </c>
+      <c r="C66" t="n">
+        <v>91773</v>
+      </c>
+      <c r="D66" t="n">
         <v>20</v>
       </c>
-      <c r="D65" t="inlineStr">
+      <c r="E66" t="inlineStr">
         <is>
           <t>Hallway</t>
         </is>
       </c>
-      <c r="E65" t="inlineStr">
-        <is>
-          <t>墙</t>
-        </is>
-      </c>
-      <c r="F65" t="n">
+      <c r="F66" t="n">
+        <v>11473</v>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>墙</t>
+        </is>
+      </c>
+      <c r="H66" t="n">
+        <v>1</v>
+      </c>
+      <c r="I66" t="n">
         <v>77</v>
       </c>
-      <c r="G65" t="n">
-        <v>1155</v>
+      <c r="J66" t="n">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="n">
+        <v>18</v>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>Bedroom</t>
+        </is>
+      </c>
+      <c r="C67" t="n">
+        <v>87188</v>
+      </c>
+      <c r="D67" t="n">
+        <v>19</v>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>Bath</t>
+        </is>
+      </c>
+      <c r="F67" t="n">
+        <v>69960</v>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>墙</t>
+        </is>
+      </c>
+      <c r="H67" t="n">
+        <v>1</v>
+      </c>
+      <c r="I67" t="n">
+        <v>212</v>
+      </c>
+      <c r="J67" t="n">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="n">
+        <v>18</v>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>Bedroom</t>
+        </is>
+      </c>
+      <c r="C68" t="n">
+        <v>87188</v>
+      </c>
+      <c r="D68" t="n">
+        <v>20</v>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>Hallway</t>
+        </is>
+      </c>
+      <c r="F68" t="n">
+        <v>11473</v>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>墙</t>
+        </is>
+      </c>
+      <c r="H68" t="n">
+        <v>1</v>
+      </c>
+      <c r="I68" t="n">
+        <v>77</v>
+      </c>
+      <c r="J68" t="n">
+        <v>15</v>
       </c>
     </row>
   </sheetData>

--- a/output/topology_excel/8422.xlsx
+++ b/output/topology_excel/8422.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J68"/>
+  <dimension ref="A1:J65"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -505,7 +505,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>窗</t>
+          <t>门</t>
         </is>
       </c>
       <c r="H2" t="n">
@@ -543,7 +543,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>窗</t>
+          <t>门</t>
         </is>
       </c>
       <c r="H3" t="n">
@@ -581,7 +581,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>窗</t>
+          <t>门</t>
         </is>
       </c>
       <c r="H4" t="n">
@@ -619,7 +619,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>窗</t>
+          <t>门</t>
         </is>
       </c>
       <c r="H5" t="n">
@@ -657,7 +657,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>窗</t>
+          <t>门</t>
         </is>
       </c>
       <c r="H6" t="n">
@@ -695,7 +695,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>窗</t>
+          <t>门</t>
         </is>
       </c>
       <c r="H7" t="n">
@@ -733,7 +733,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>窗</t>
+          <t>门</t>
         </is>
       </c>
       <c r="H8" t="n">
@@ -771,7 +771,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>窗</t>
+          <t>门</t>
         </is>
       </c>
       <c r="H9" t="n">
@@ -809,7 +809,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>窗</t>
+          <t>门</t>
         </is>
       </c>
       <c r="H10" t="n">
@@ -847,7 +847,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>窗</t>
+          <t>门</t>
         </is>
       </c>
       <c r="H11" t="n">
@@ -885,7 +885,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>窗</t>
+          <t>门</t>
         </is>
       </c>
       <c r="H12" t="n">
@@ -923,7 +923,7 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>窗</t>
+          <t>门</t>
         </is>
       </c>
       <c r="H13" t="n">
@@ -961,7 +961,7 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>窗</t>
+          <t>门</t>
         </is>
       </c>
       <c r="H14" t="n">
@@ -999,7 +999,7 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>窗</t>
+          <t>门</t>
         </is>
       </c>
       <c r="H15" t="n">
@@ -1037,7 +1037,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>窗</t>
+          <t>门</t>
         </is>
       </c>
       <c r="H16" t="n">
@@ -1075,7 +1075,7 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>窗</t>
+          <t>门</t>
         </is>
       </c>
       <c r="H17" t="n">
@@ -1113,7 +1113,7 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>窗</t>
+          <t>门</t>
         </is>
       </c>
       <c r="H18" t="n">
@@ -1151,7 +1151,7 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>窗</t>
+          <t>门</t>
         </is>
       </c>
       <c r="H19" t="n">
@@ -1189,7 +1189,7 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>窗</t>
+          <t>门</t>
         </is>
       </c>
       <c r="H20" t="n">
@@ -1291,15 +1291,15 @@
         <v>143869</v>
       </c>
       <c r="D23" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Living Room</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="F23" t="n">
-        <v>234855</v>
+        <v>30488</v>
       </c>
       <c r="G23" t="inlineStr">
         <is>
@@ -1310,10 +1310,10 @@
         <v>1</v>
       </c>
       <c r="I23" t="n">
-        <v>200</v>
+        <v>206</v>
       </c>
       <c r="J23" t="n">
-        <v>17</v>
+        <v>25</v>
       </c>
     </row>
     <row r="24">
@@ -1329,15 +1329,15 @@
         <v>143869</v>
       </c>
       <c r="D24" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Hallway</t>
         </is>
       </c>
       <c r="F24" t="n">
-        <v>30488</v>
+        <v>54021</v>
       </c>
       <c r="G24" t="inlineStr">
         <is>
@@ -1348,7 +1348,7 @@
         <v>1</v>
       </c>
       <c r="I24" t="n">
-        <v>206</v>
+        <v>41</v>
       </c>
       <c r="J24" t="n">
         <v>25</v>
@@ -1356,26 +1356,26 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Kitchen</t>
+          <t>Living Room</t>
         </is>
       </c>
       <c r="C25" t="n">
-        <v>143869</v>
+        <v>234855</v>
       </c>
       <c r="D25" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Hallway</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="F25" t="n">
-        <v>54021</v>
+        <v>32412</v>
       </c>
       <c r="G25" t="inlineStr">
         <is>
@@ -1386,10 +1386,10 @@
         <v>1</v>
       </c>
       <c r="I25" t="n">
-        <v>41</v>
+        <v>219</v>
       </c>
       <c r="J25" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
     </row>
     <row r="26">
@@ -1405,7 +1405,7 @@
         <v>234855</v>
       </c>
       <c r="D26" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
@@ -1413,7 +1413,7 @@
         </is>
       </c>
       <c r="F26" t="n">
-        <v>32412</v>
+        <v>30488</v>
       </c>
       <c r="G26" t="inlineStr">
         <is>
@@ -1424,7 +1424,7 @@
         <v>1</v>
       </c>
       <c r="I26" t="n">
-        <v>219</v>
+        <v>83</v>
       </c>
       <c r="J26" t="n">
         <v>27</v>
@@ -1443,15 +1443,15 @@
         <v>234855</v>
       </c>
       <c r="D27" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Hallway</t>
         </is>
       </c>
       <c r="F27" t="n">
-        <v>30488</v>
+        <v>15768</v>
       </c>
       <c r="G27" t="inlineStr">
         <is>
@@ -1462,10 +1462,10 @@
         <v>1</v>
       </c>
       <c r="I27" t="n">
-        <v>142</v>
+        <v>163</v>
       </c>
       <c r="J27" t="n">
-        <v>100</v>
+        <v>125</v>
       </c>
     </row>
     <row r="28">
@@ -1481,15 +1481,15 @@
         <v>234855</v>
       </c>
       <c r="D28" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Hallway</t>
+          <t>Bath</t>
         </is>
       </c>
       <c r="F28" t="n">
-        <v>15768</v>
+        <v>11172</v>
       </c>
       <c r="G28" t="inlineStr">
         <is>
@@ -1500,10 +1500,10 @@
         <v>1</v>
       </c>
       <c r="I28" t="n">
-        <v>163</v>
+        <v>131</v>
       </c>
       <c r="J28" t="n">
-        <v>125</v>
+        <v>115</v>
       </c>
     </row>
     <row r="29">
@@ -1519,15 +1519,15 @@
         <v>234855</v>
       </c>
       <c r="D29" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Kitchen</t>
+          <t>Hallway</t>
         </is>
       </c>
       <c r="F29" t="n">
-        <v>59944</v>
+        <v>54021</v>
       </c>
       <c r="G29" t="inlineStr">
         <is>
@@ -1538,10 +1538,10 @@
         <v>1</v>
       </c>
       <c r="I29" t="n">
-        <v>416</v>
+        <v>175</v>
       </c>
       <c r="J29" t="n">
-        <v>163</v>
+        <v>17</v>
       </c>
     </row>
     <row r="30">
@@ -1557,15 +1557,15 @@
         <v>234855</v>
       </c>
       <c r="D30" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Bath</t>
+          <t>Kitchen</t>
         </is>
       </c>
       <c r="F30" t="n">
-        <v>11172</v>
+        <v>59944</v>
       </c>
       <c r="G30" t="inlineStr">
         <is>
@@ -1576,10 +1576,10 @@
         <v>1</v>
       </c>
       <c r="I30" t="n">
-        <v>131</v>
+        <v>253</v>
       </c>
       <c r="J30" t="n">
-        <v>115</v>
+        <v>146</v>
       </c>
     </row>
     <row r="31">
@@ -1595,15 +1595,15 @@
         <v>234855</v>
       </c>
       <c r="D31" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Hallway</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="F31" t="n">
-        <v>54021</v>
+        <v>21024</v>
       </c>
       <c r="G31" t="inlineStr">
         <is>
@@ -1614,10 +1614,10 @@
         <v>1</v>
       </c>
       <c r="I31" t="n">
-        <v>175</v>
+        <v>72</v>
       </c>
       <c r="J31" t="n">
-        <v>17</v>
+        <v>26</v>
       </c>
     </row>
     <row r="32">
@@ -1633,15 +1633,15 @@
         <v>234855</v>
       </c>
       <c r="D32" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Bedroom</t>
         </is>
       </c>
       <c r="F32" t="n">
-        <v>21024</v>
+        <v>141052</v>
       </c>
       <c r="G32" t="inlineStr">
         <is>
@@ -1652,34 +1652,34 @@
         <v>1</v>
       </c>
       <c r="I32" t="n">
-        <v>72</v>
+        <v>123</v>
       </c>
       <c r="J32" t="n">
-        <v>26</v>
+        <v>17</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Living Room</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="C33" t="n">
-        <v>234855</v>
+        <v>32412</v>
       </c>
       <c r="D33" t="n">
-        <v>16</v>
+        <v>5</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Bedroom</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="F33" t="n">
-        <v>141052</v>
+        <v>30488</v>
       </c>
       <c r="G33" t="inlineStr">
         <is>
@@ -1690,7 +1690,7 @@
         <v>1</v>
       </c>
       <c r="I33" t="n">
-        <v>123</v>
+        <v>148</v>
       </c>
       <c r="J33" t="n">
         <v>17</v>
@@ -1698,26 +1698,26 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Living Room</t>
         </is>
       </c>
       <c r="C34" t="n">
-        <v>32412</v>
+        <v>313405</v>
       </c>
       <c r="D34" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Hallway</t>
         </is>
       </c>
       <c r="F34" t="n">
-        <v>30488</v>
+        <v>54021</v>
       </c>
       <c r="G34" t="inlineStr">
         <is>
@@ -1728,10 +1728,10 @@
         <v>1</v>
       </c>
       <c r="I34" t="n">
-        <v>148</v>
+        <v>84</v>
       </c>
       <c r="J34" t="n">
-        <v>17</v>
+        <v>21</v>
       </c>
     </row>
     <row r="35">
@@ -1747,15 +1747,15 @@
         <v>313405</v>
       </c>
       <c r="D35" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Hallway</t>
+          <t>Bedroom</t>
         </is>
       </c>
       <c r="F35" t="n">
-        <v>54021</v>
+        <v>91155</v>
       </c>
       <c r="G35" t="inlineStr">
         <is>
@@ -1766,10 +1766,10 @@
         <v>1</v>
       </c>
       <c r="I35" t="n">
-        <v>84</v>
+        <v>322</v>
       </c>
       <c r="J35" t="n">
-        <v>21</v>
+        <v>311</v>
       </c>
     </row>
     <row r="36">
@@ -1785,15 +1785,15 @@
         <v>313405</v>
       </c>
       <c r="D36" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Bedroom</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="F36" t="n">
-        <v>91155</v>
+        <v>37682</v>
       </c>
       <c r="G36" t="inlineStr">
         <is>
@@ -1804,10 +1804,10 @@
         <v>1</v>
       </c>
       <c r="I36" t="n">
-        <v>322</v>
+        <v>166</v>
       </c>
       <c r="J36" t="n">
-        <v>311</v>
+        <v>18</v>
       </c>
     </row>
     <row r="37">
@@ -1823,15 +1823,15 @@
         <v>313405</v>
       </c>
       <c r="D37" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Storage</t>
         </is>
       </c>
       <c r="F37" t="n">
-        <v>37682</v>
+        <v>14732</v>
       </c>
       <c r="G37" t="inlineStr">
         <is>
@@ -1842,10 +1842,10 @@
         <v>1</v>
       </c>
       <c r="I37" t="n">
-        <v>329</v>
+        <v>142</v>
       </c>
       <c r="J37" t="n">
-        <v>147</v>
+        <v>134</v>
       </c>
     </row>
     <row r="38">
@@ -1861,15 +1861,15 @@
         <v>313405</v>
       </c>
       <c r="D38" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Storage</t>
+          <t>Bath</t>
         </is>
       </c>
       <c r="F38" t="n">
-        <v>14732</v>
+        <v>14097</v>
       </c>
       <c r="G38" t="inlineStr">
         <is>
@@ -1880,10 +1880,10 @@
         <v>1</v>
       </c>
       <c r="I38" t="n">
-        <v>142</v>
+        <v>111</v>
       </c>
       <c r="J38" t="n">
-        <v>134</v>
+        <v>15</v>
       </c>
     </row>
     <row r="39">
@@ -1899,15 +1899,15 @@
         <v>313405</v>
       </c>
       <c r="D39" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Bath</t>
+          <t>Bedroom</t>
         </is>
       </c>
       <c r="F39" t="n">
-        <v>14097</v>
+        <v>91773</v>
       </c>
       <c r="G39" t="inlineStr">
         <is>
@@ -1918,10 +1918,10 @@
         <v>1</v>
       </c>
       <c r="I39" t="n">
-        <v>111</v>
+        <v>159</v>
       </c>
       <c r="J39" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
     </row>
     <row r="40">
@@ -1937,7 +1937,7 @@
         <v>313405</v>
       </c>
       <c r="D40" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
@@ -1945,7 +1945,7 @@
         </is>
       </c>
       <c r="F40" t="n">
-        <v>91773</v>
+        <v>87188</v>
       </c>
       <c r="G40" t="inlineStr">
         <is>
@@ -1956,10 +1956,10 @@
         <v>1</v>
       </c>
       <c r="I40" t="n">
-        <v>159</v>
+        <v>146</v>
       </c>
       <c r="J40" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
     </row>
     <row r="41">
@@ -1975,15 +1975,15 @@
         <v>313405</v>
       </c>
       <c r="D41" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Bedroom</t>
+          <t>Hallway</t>
         </is>
       </c>
       <c r="F41" t="n">
-        <v>87188</v>
+        <v>11473</v>
       </c>
       <c r="G41" t="inlineStr">
         <is>
@@ -1994,34 +1994,34 @@
         <v>1</v>
       </c>
       <c r="I41" t="n">
-        <v>146</v>
+        <v>149</v>
       </c>
       <c r="J41" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Living Room</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="C42" t="n">
-        <v>313405</v>
+        <v>30488</v>
       </c>
       <c r="D42" t="n">
-        <v>20</v>
+        <v>7</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Hallway</t>
+          <t>Bath</t>
         </is>
       </c>
       <c r="F42" t="n">
-        <v>11473</v>
+        <v>11172</v>
       </c>
       <c r="G42" t="inlineStr">
         <is>
@@ -2032,10 +2032,10 @@
         <v>1</v>
       </c>
       <c r="I42" t="n">
-        <v>149</v>
+        <v>106</v>
       </c>
       <c r="J42" t="n">
-        <v>17</v>
+        <v>27</v>
       </c>
     </row>
     <row r="43">
@@ -2051,15 +2051,15 @@
         <v>30488</v>
       </c>
       <c r="D43" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Bath</t>
+          <t>Hallway</t>
         </is>
       </c>
       <c r="F43" t="n">
-        <v>11172</v>
+        <v>54021</v>
       </c>
       <c r="G43" t="inlineStr">
         <is>
@@ -2070,34 +2070,34 @@
         <v>1</v>
       </c>
       <c r="I43" t="n">
-        <v>106</v>
+        <v>148</v>
       </c>
       <c r="J43" t="n">
-        <v>27</v>
+        <v>25</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Hallway</t>
         </is>
       </c>
       <c r="C44" t="n">
-        <v>30488</v>
+        <v>15768</v>
       </c>
       <c r="D44" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Hallway</t>
+          <t>Kitchen</t>
         </is>
       </c>
       <c r="F44" t="n">
-        <v>54021</v>
+        <v>59944</v>
       </c>
       <c r="G44" t="inlineStr">
         <is>
@@ -2108,34 +2108,34 @@
         <v>1</v>
       </c>
       <c r="I44" t="n">
-        <v>148</v>
+        <v>108</v>
       </c>
       <c r="J44" t="n">
-        <v>25</v>
+        <v>17</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B45" t="inlineStr">
         <is>
+          <t>Bath</t>
+        </is>
+      </c>
+      <c r="C45" t="n">
+        <v>11172</v>
+      </c>
+      <c r="D45" t="n">
+        <v>8</v>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
           <t>Hallway</t>
         </is>
       </c>
-      <c r="C45" t="n">
-        <v>15768</v>
-      </c>
-      <c r="D45" t="n">
-        <v>9</v>
-      </c>
-      <c r="E45" t="inlineStr">
-        <is>
-          <t>Kitchen</t>
-        </is>
-      </c>
       <c r="F45" t="n">
-        <v>59944</v>
+        <v>54021</v>
       </c>
       <c r="G45" t="inlineStr">
         <is>
@@ -2146,7 +2146,7 @@
         <v>1</v>
       </c>
       <c r="I45" t="n">
-        <v>108</v>
+        <v>98</v>
       </c>
       <c r="J45" t="n">
         <v>17</v>
@@ -2154,26 +2154,26 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Bath</t>
+          <t>Hallway</t>
         </is>
       </c>
       <c r="C46" t="n">
-        <v>11172</v>
+        <v>54021</v>
       </c>
       <c r="D46" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Hallway</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="F46" t="n">
-        <v>54021</v>
+        <v>37682</v>
       </c>
       <c r="G46" t="inlineStr">
         <is>
@@ -2184,10 +2184,10 @@
         <v>1</v>
       </c>
       <c r="I46" t="n">
-        <v>98</v>
+        <v>21</v>
       </c>
       <c r="J46" t="n">
-        <v>17</v>
+        <v>21</v>
       </c>
     </row>
     <row r="47">
@@ -2203,7 +2203,7 @@
         <v>54021</v>
       </c>
       <c r="D47" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="E47" t="inlineStr">
         <is>
@@ -2211,7 +2211,7 @@
         </is>
       </c>
       <c r="F47" t="n">
-        <v>37682</v>
+        <v>47304</v>
       </c>
       <c r="G47" t="inlineStr">
         <is>
@@ -2222,7 +2222,7 @@
         <v>1</v>
       </c>
       <c r="I47" t="n">
-        <v>123</v>
+        <v>216</v>
       </c>
       <c r="J47" t="n">
         <v>73</v>
@@ -2241,7 +2241,7 @@
         <v>54021</v>
       </c>
       <c r="D48" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="E48" t="inlineStr">
         <is>
@@ -2249,7 +2249,7 @@
         </is>
       </c>
       <c r="F48" t="n">
-        <v>47304</v>
+        <v>21024</v>
       </c>
       <c r="G48" t="inlineStr">
         <is>
@@ -2260,34 +2260,34 @@
         <v>1</v>
       </c>
       <c r="I48" t="n">
-        <v>216</v>
+        <v>96</v>
       </c>
       <c r="J48" t="n">
-        <v>73</v>
+        <v>21</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Hallway</t>
+          <t>Kitchen</t>
         </is>
       </c>
       <c r="C49" t="n">
-        <v>54021</v>
+        <v>59944</v>
       </c>
       <c r="D49" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Bedroom</t>
         </is>
       </c>
       <c r="F49" t="n">
-        <v>21024</v>
+        <v>141052</v>
       </c>
       <c r="G49" t="inlineStr">
         <is>
@@ -2298,26 +2298,26 @@
         <v>1</v>
       </c>
       <c r="I49" t="n">
-        <v>96</v>
+        <v>254</v>
       </c>
       <c r="J49" t="n">
-        <v>21</v>
+        <v>17</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Kitchen</t>
+          <t>Bedroom</t>
         </is>
       </c>
       <c r="C50" t="n">
-        <v>59944</v>
+        <v>91155</v>
       </c>
       <c r="D50" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="E50" t="inlineStr">
         <is>
@@ -2325,7 +2325,7 @@
         </is>
       </c>
       <c r="F50" t="n">
-        <v>141052</v>
+        <v>91773</v>
       </c>
       <c r="G50" t="inlineStr">
         <is>
@@ -2336,7 +2336,7 @@
         <v>1</v>
       </c>
       <c r="I50" t="n">
-        <v>254</v>
+        <v>309</v>
       </c>
       <c r="J50" t="n">
         <v>17</v>
@@ -2344,26 +2344,26 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Bedroom</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="C51" t="n">
-        <v>91155</v>
+        <v>37682</v>
       </c>
       <c r="D51" t="n">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Bedroom</t>
+          <t>Storage</t>
         </is>
       </c>
       <c r="F51" t="n">
-        <v>91773</v>
+        <v>14732</v>
       </c>
       <c r="G51" t="inlineStr">
         <is>
@@ -2374,10 +2374,10 @@
         <v>1</v>
       </c>
       <c r="I51" t="n">
-        <v>309</v>
+        <v>116</v>
       </c>
       <c r="J51" t="n">
-        <v>17</v>
+        <v>21</v>
       </c>
     </row>
     <row r="52">
@@ -2393,15 +2393,15 @@
         <v>37682</v>
       </c>
       <c r="D52" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Storage</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="F52" t="n">
-        <v>14732</v>
+        <v>47304</v>
       </c>
       <c r="G52" t="inlineStr">
         <is>
@@ -2412,7 +2412,7 @@
         <v>1</v>
       </c>
       <c r="I52" t="n">
-        <v>116</v>
+        <v>133</v>
       </c>
       <c r="J52" t="n">
         <v>21</v>
@@ -2431,15 +2431,15 @@
         <v>37682</v>
       </c>
       <c r="D53" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Bath</t>
         </is>
       </c>
       <c r="F53" t="n">
-        <v>47304</v>
+        <v>14097</v>
       </c>
       <c r="G53" t="inlineStr">
         <is>
@@ -2450,7 +2450,7 @@
         <v>1</v>
       </c>
       <c r="I53" t="n">
-        <v>133</v>
+        <v>98</v>
       </c>
       <c r="J53" t="n">
         <v>21</v>
@@ -2469,15 +2469,15 @@
         <v>37682</v>
       </c>
       <c r="D54" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Bath</t>
+          <t>Bedroom</t>
         </is>
       </c>
       <c r="F54" t="n">
-        <v>14097</v>
+        <v>87188</v>
       </c>
       <c r="G54" t="inlineStr">
         <is>
@@ -2488,34 +2488,34 @@
         <v>1</v>
       </c>
       <c r="I54" t="n">
-        <v>98</v>
+        <v>159</v>
       </c>
       <c r="J54" t="n">
-        <v>21</v>
+        <v>30</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Storage</t>
         </is>
       </c>
       <c r="C55" t="n">
-        <v>37682</v>
+        <v>14732</v>
       </c>
       <c r="D55" t="n">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Bedroom</t>
+          <t>Bath</t>
         </is>
       </c>
       <c r="F55" t="n">
-        <v>87188</v>
+        <v>14097</v>
       </c>
       <c r="G55" t="inlineStr">
         <is>
@@ -2526,34 +2526,34 @@
         <v>1</v>
       </c>
       <c r="I55" t="n">
-        <v>159</v>
+        <v>127</v>
       </c>
       <c r="J55" t="n">
-        <v>30</v>
+        <v>13</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Storage</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="C56" t="n">
-        <v>14732</v>
+        <v>21024</v>
       </c>
       <c r="D56" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Bath</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="F56" t="n">
-        <v>14097</v>
+        <v>47304</v>
       </c>
       <c r="G56" t="inlineStr">
         <is>
@@ -2564,10 +2564,10 @@
         <v>1</v>
       </c>
       <c r="I56" t="n">
-        <v>127</v>
+        <v>219</v>
       </c>
       <c r="J56" t="n">
-        <v>13</v>
+        <v>18</v>
       </c>
     </row>
     <row r="57">
@@ -2583,15 +2583,15 @@
         <v>21024</v>
       </c>
       <c r="D57" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Bedroom</t>
         </is>
       </c>
       <c r="F57" t="n">
-        <v>47304</v>
+        <v>141052</v>
       </c>
       <c r="G57" t="inlineStr">
         <is>
@@ -2602,10 +2602,10 @@
         <v>1</v>
       </c>
       <c r="I57" t="n">
-        <v>219</v>
+        <v>130</v>
       </c>
       <c r="J57" t="n">
-        <v>18</v>
+        <v>26</v>
       </c>
     </row>
     <row r="58">
@@ -2621,34 +2621,34 @@
         <v>21024</v>
       </c>
       <c r="D58" t="n">
+        <v>19</v>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>Bath</t>
+        </is>
+      </c>
+      <c r="F58" t="n">
+        <v>69960</v>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>墙</t>
+        </is>
+      </c>
+      <c r="H58" t="n">
+        <v>1</v>
+      </c>
+      <c r="I58" t="n">
+        <v>96</v>
+      </c>
+      <c r="J58" t="n">
         <v>16</v>
-      </c>
-      <c r="E58" t="inlineStr">
-        <is>
-          <t>Bedroom</t>
-        </is>
-      </c>
-      <c r="F58" t="n">
-        <v>141052</v>
-      </c>
-      <c r="G58" t="inlineStr">
-        <is>
-          <t>墙</t>
-        </is>
-      </c>
-      <c r="H58" t="n">
-        <v>1</v>
-      </c>
-      <c r="I58" t="n">
-        <v>130</v>
-      </c>
-      <c r="J58" t="n">
-        <v>26</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B59" t="inlineStr">
         <is>
@@ -2656,18 +2656,18 @@
         </is>
       </c>
       <c r="C59" t="n">
-        <v>21024</v>
+        <v>47304</v>
       </c>
       <c r="D59" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Bath</t>
+          <t>Bedroom</t>
         </is>
       </c>
       <c r="F59" t="n">
-        <v>69960</v>
+        <v>87188</v>
       </c>
       <c r="G59" t="inlineStr">
         <is>
@@ -2678,10 +2678,10 @@
         <v>1</v>
       </c>
       <c r="I59" t="n">
-        <v>96</v>
+        <v>56</v>
       </c>
       <c r="J59" t="n">
-        <v>16</v>
+        <v>28</v>
       </c>
     </row>
     <row r="60">
@@ -2697,7 +2697,7 @@
         <v>47304</v>
       </c>
       <c r="D60" t="n">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="E60" t="inlineStr">
         <is>
@@ -2705,7 +2705,7 @@
         </is>
       </c>
       <c r="F60" t="n">
-        <v>14097</v>
+        <v>69960</v>
       </c>
       <c r="G60" t="inlineStr">
         <is>
@@ -2716,23 +2716,23 @@
         <v>1</v>
       </c>
       <c r="I60" t="n">
-        <v>208</v>
+        <v>216</v>
       </c>
       <c r="J60" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Bath</t>
         </is>
       </c>
       <c r="C61" t="n">
-        <v>47304</v>
+        <v>14097</v>
       </c>
       <c r="D61" t="n">
         <v>18</v>
@@ -2754,23 +2754,23 @@
         <v>1</v>
       </c>
       <c r="I61" t="n">
-        <v>56</v>
+        <v>127</v>
       </c>
       <c r="J61" t="n">
-        <v>28</v>
+        <v>17</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Bedroom</t>
         </is>
       </c>
       <c r="C62" t="n">
-        <v>47304</v>
+        <v>141052</v>
       </c>
       <c r="D62" t="n">
         <v>19</v>
@@ -2792,34 +2792,34 @@
         <v>1</v>
       </c>
       <c r="I62" t="n">
-        <v>216</v>
+        <v>212</v>
       </c>
       <c r="J62" t="n">
-        <v>16</v>
+        <v>26</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Bath</t>
+          <t>Bedroom</t>
         </is>
       </c>
       <c r="C63" t="n">
-        <v>14097</v>
+        <v>91773</v>
       </c>
       <c r="D63" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Bedroom</t>
+          <t>Hallway</t>
         </is>
       </c>
       <c r="F63" t="n">
-        <v>87188</v>
+        <v>11473</v>
       </c>
       <c r="G63" t="inlineStr">
         <is>
@@ -2830,15 +2830,15 @@
         <v>1</v>
       </c>
       <c r="I63" t="n">
-        <v>127</v>
+        <v>77</v>
       </c>
       <c r="J63" t="n">
-        <v>17</v>
+        <v>13</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="B64" t="inlineStr">
         <is>
@@ -2846,7 +2846,7 @@
         </is>
       </c>
       <c r="C64" t="n">
-        <v>141052</v>
+        <v>87188</v>
       </c>
       <c r="D64" t="n">
         <v>19</v>
@@ -2871,12 +2871,12 @@
         <v>212</v>
       </c>
       <c r="J64" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B65" t="inlineStr">
         <is>
@@ -2884,18 +2884,18 @@
         </is>
       </c>
       <c r="C65" t="n">
-        <v>91773</v>
+        <v>87188</v>
       </c>
       <c r="D65" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Bedroom</t>
+          <t>Hallway</t>
         </is>
       </c>
       <c r="F65" t="n">
-        <v>87188</v>
+        <v>11473</v>
       </c>
       <c r="G65" t="inlineStr">
         <is>
@@ -2906,123 +2906,9 @@
         <v>1</v>
       </c>
       <c r="I65" t="n">
-        <v>177</v>
+        <v>77</v>
       </c>
       <c r="J65" t="n">
-        <v>119</v>
-      </c>
-    </row>
-    <row r="66">
-      <c r="A66" t="n">
-        <v>17</v>
-      </c>
-      <c r="B66" t="inlineStr">
-        <is>
-          <t>Bedroom</t>
-        </is>
-      </c>
-      <c r="C66" t="n">
-        <v>91773</v>
-      </c>
-      <c r="D66" t="n">
-        <v>20</v>
-      </c>
-      <c r="E66" t="inlineStr">
-        <is>
-          <t>Hallway</t>
-        </is>
-      </c>
-      <c r="F66" t="n">
-        <v>11473</v>
-      </c>
-      <c r="G66" t="inlineStr">
-        <is>
-          <t>墙</t>
-        </is>
-      </c>
-      <c r="H66" t="n">
-        <v>1</v>
-      </c>
-      <c r="I66" t="n">
-        <v>77</v>
-      </c>
-      <c r="J66" t="n">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="67">
-      <c r="A67" t="n">
-        <v>18</v>
-      </c>
-      <c r="B67" t="inlineStr">
-        <is>
-          <t>Bedroom</t>
-        </is>
-      </c>
-      <c r="C67" t="n">
-        <v>87188</v>
-      </c>
-      <c r="D67" t="n">
-        <v>19</v>
-      </c>
-      <c r="E67" t="inlineStr">
-        <is>
-          <t>Bath</t>
-        </is>
-      </c>
-      <c r="F67" t="n">
-        <v>69960</v>
-      </c>
-      <c r="G67" t="inlineStr">
-        <is>
-          <t>墙</t>
-        </is>
-      </c>
-      <c r="H67" t="n">
-        <v>1</v>
-      </c>
-      <c r="I67" t="n">
-        <v>212</v>
-      </c>
-      <c r="J67" t="n">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="68">
-      <c r="A68" t="n">
-        <v>18</v>
-      </c>
-      <c r="B68" t="inlineStr">
-        <is>
-          <t>Bedroom</t>
-        </is>
-      </c>
-      <c r="C68" t="n">
-        <v>87188</v>
-      </c>
-      <c r="D68" t="n">
-        <v>20</v>
-      </c>
-      <c r="E68" t="inlineStr">
-        <is>
-          <t>Hallway</t>
-        </is>
-      </c>
-      <c r="F68" t="n">
-        <v>11473</v>
-      </c>
-      <c r="G68" t="inlineStr">
-        <is>
-          <t>墙</t>
-        </is>
-      </c>
-      <c r="H68" t="n">
-        <v>1</v>
-      </c>
-      <c r="I68" t="n">
-        <v>77</v>
-      </c>
-      <c r="J68" t="n">
         <v>15</v>
       </c>
     </row>

--- a/output/topology_excel/8422.xlsx
+++ b/output/topology_excel/8422.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F65"/>
+  <dimension ref="A1:F73"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -465,7 +465,7 @@
         <v>1</v>
       </c>
       <c r="B2" t="n">
-        <v>3</v>
+        <v>18</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -484,10 +484,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="B3" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -506,10 +506,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="B4" t="n">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -528,10 +528,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="B5" t="n">
-        <v>8</v>
+        <v>19</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -553,7 +553,7 @@
         <v>1</v>
       </c>
       <c r="B6" t="n">
-        <v>4</v>
+        <v>14</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -572,10 +572,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>4</v>
+        <v>14</v>
       </c>
       <c r="B7" t="n">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -594,10 +594,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="B8" t="n">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -616,10 +616,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>4</v>
+        <v>14</v>
       </c>
       <c r="B9" t="n">
-        <v>11</v>
+        <v>20</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -641,7 +641,7 @@
         <v>2</v>
       </c>
       <c r="B10" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -660,10 +660,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>4</v>
+        <v>14</v>
       </c>
       <c r="B11" t="n">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -682,10 +682,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="B12" t="n">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -704,10 +704,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B13" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -726,10 +726,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="B14" t="n">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -748,10 +748,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="B15" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -770,10 +770,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="B16" t="n">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -792,10 +792,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="B17" t="n">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -814,10 +814,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="B18" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -836,10 +836,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="B19" t="n">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -858,10 +858,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>4</v>
+        <v>14</v>
       </c>
       <c r="B20" t="n">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -883,7 +883,7 @@
         <v>1</v>
       </c>
       <c r="B21" t="n">
-        <v>3</v>
+        <v>18</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -916,10 +916,10 @@
         <v>1</v>
       </c>
       <c r="E22" t="n">
-        <v>376</v>
+        <v>360</v>
       </c>
       <c r="F22" t="n">
-        <v>273</v>
+        <v>16</v>
       </c>
     </row>
     <row r="23">
@@ -927,7 +927,7 @@
         <v>1</v>
       </c>
       <c r="B23" t="n">
-        <v>5</v>
+        <v>19</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -949,7 +949,7 @@
         <v>1</v>
       </c>
       <c r="B24" t="n">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -968,10 +968,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B25" t="n">
-        <v>3</v>
+        <v>14</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -982,10 +982,10 @@
         <v>1</v>
       </c>
       <c r="E25" t="n">
-        <v>219</v>
+        <v>257</v>
       </c>
       <c r="F25" t="n">
-        <v>27</v>
+        <v>16</v>
       </c>
     </row>
     <row r="26">
@@ -993,7 +993,7 @@
         <v>2</v>
       </c>
       <c r="B26" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -1004,10 +1004,10 @@
         <v>1</v>
       </c>
       <c r="E26" t="n">
-        <v>83</v>
+        <v>108</v>
       </c>
       <c r="F26" t="n">
-        <v>27</v>
+        <v>17</v>
       </c>
     </row>
     <row r="27">
@@ -1015,7 +1015,7 @@
         <v>2</v>
       </c>
       <c r="B27" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -1026,10 +1026,10 @@
         <v>1</v>
       </c>
       <c r="E27" t="n">
-        <v>163</v>
+        <v>253</v>
       </c>
       <c r="F27" t="n">
-        <v>125</v>
+        <v>146</v>
       </c>
     </row>
     <row r="28">
@@ -1037,7 +1037,7 @@
         <v>2</v>
       </c>
       <c r="B28" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -1048,18 +1048,18 @@
         <v>1</v>
       </c>
       <c r="E28" t="n">
-        <v>131</v>
+        <v>254</v>
       </c>
       <c r="F28" t="n">
-        <v>115</v>
+        <v>17</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B29" t="n">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -1070,18 +1070,18 @@
         <v>1</v>
       </c>
       <c r="E29" t="n">
-        <v>175</v>
+        <v>219</v>
       </c>
       <c r="F29" t="n">
-        <v>17</v>
+        <v>27</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B30" t="n">
-        <v>9</v>
+        <v>19</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -1092,15 +1092,15 @@
         <v>1</v>
       </c>
       <c r="E30" t="n">
-        <v>253</v>
+        <v>83</v>
       </c>
       <c r="F30" t="n">
-        <v>146</v>
+        <v>27</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B31" t="n">
         <v>13</v>
@@ -1114,18 +1114,18 @@
         <v>1</v>
       </c>
       <c r="E31" t="n">
-        <v>72</v>
+        <v>108</v>
       </c>
       <c r="F31" t="n">
-        <v>26</v>
+        <v>17</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B32" t="n">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -1136,7 +1136,7 @@
         <v>1</v>
       </c>
       <c r="E32" t="n">
-        <v>123</v>
+        <v>146</v>
       </c>
       <c r="F32" t="n">
         <v>17</v>
@@ -1147,7 +1147,7 @@
         <v>3</v>
       </c>
       <c r="B33" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -1158,7 +1158,7 @@
         <v>1</v>
       </c>
       <c r="E33" t="n">
-        <v>148</v>
+        <v>98</v>
       </c>
       <c r="F33" t="n">
         <v>17</v>
@@ -1169,7 +1169,7 @@
         <v>4</v>
       </c>
       <c r="B34" t="n">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -1180,10 +1180,10 @@
         <v>1</v>
       </c>
       <c r="E34" t="n">
-        <v>84</v>
+        <v>39</v>
       </c>
       <c r="F34" t="n">
-        <v>21</v>
+        <v>16</v>
       </c>
     </row>
     <row r="35">
@@ -1191,7 +1191,7 @@
         <v>4</v>
       </c>
       <c r="B35" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -1202,18 +1202,18 @@
         <v>1</v>
       </c>
       <c r="E35" t="n">
-        <v>322</v>
+        <v>309</v>
       </c>
       <c r="F35" t="n">
-        <v>311</v>
+        <v>16</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B36" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -1224,18 +1224,18 @@
         <v>1</v>
       </c>
       <c r="E36" t="n">
-        <v>166</v>
+        <v>295</v>
       </c>
       <c r="F36" t="n">
-        <v>18</v>
+        <v>13</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B37" t="n">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -1246,18 +1246,18 @@
         <v>1</v>
       </c>
       <c r="E37" t="n">
-        <v>142</v>
+        <v>309</v>
       </c>
       <c r="F37" t="n">
-        <v>134</v>
+        <v>17</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="B38" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -1268,18 +1268,18 @@
         <v>1</v>
       </c>
       <c r="E38" t="n">
-        <v>111</v>
+        <v>123</v>
       </c>
       <c r="F38" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="B39" t="n">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -1290,18 +1290,18 @@
         <v>1</v>
       </c>
       <c r="E39" t="n">
-        <v>159</v>
+        <v>130</v>
       </c>
       <c r="F39" t="n">
-        <v>13</v>
+        <v>26</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="B40" t="n">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -1312,18 +1312,18 @@
         <v>1</v>
       </c>
       <c r="E40" t="n">
-        <v>146</v>
+        <v>212</v>
       </c>
       <c r="F40" t="n">
-        <v>15</v>
+        <v>26</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="B41" t="n">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -1334,18 +1334,18 @@
         <v>1</v>
       </c>
       <c r="E41" t="n">
-        <v>149</v>
+        <v>159</v>
       </c>
       <c r="F41" t="n">
-        <v>17</v>
+        <v>13</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="B42" t="n">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -1356,18 +1356,18 @@
         <v>1</v>
       </c>
       <c r="E42" t="n">
-        <v>106</v>
+        <v>77</v>
       </c>
       <c r="F42" t="n">
-        <v>27</v>
+        <v>13</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="B43" t="n">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -1378,18 +1378,18 @@
         <v>1</v>
       </c>
       <c r="E43" t="n">
-        <v>148</v>
+        <v>159</v>
       </c>
       <c r="F43" t="n">
-        <v>25</v>
+        <v>30</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="B44" t="n">
-        <v>9</v>
+        <v>22</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -1400,18 +1400,18 @@
         <v>1</v>
       </c>
       <c r="E44" t="n">
-        <v>108</v>
+        <v>56</v>
       </c>
       <c r="F44" t="n">
-        <v>17</v>
+        <v>28</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B45" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -1422,7 +1422,7 @@
         <v>1</v>
       </c>
       <c r="E45" t="n">
-        <v>98</v>
+        <v>127</v>
       </c>
       <c r="F45" t="n">
         <v>17</v>
@@ -1433,7 +1433,7 @@
         <v>8</v>
       </c>
       <c r="B46" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -1444,10 +1444,10 @@
         <v>1</v>
       </c>
       <c r="E46" t="n">
-        <v>21</v>
+        <v>146</v>
       </c>
       <c r="F46" t="n">
-        <v>21</v>
+        <v>15</v>
       </c>
     </row>
     <row r="47">
@@ -1455,7 +1455,7 @@
         <v>8</v>
       </c>
       <c r="B47" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -1466,10 +1466,10 @@
         <v>1</v>
       </c>
       <c r="E47" t="n">
-        <v>216</v>
+        <v>212</v>
       </c>
       <c r="F47" t="n">
-        <v>73</v>
+        <v>28</v>
       </c>
     </row>
     <row r="48">
@@ -1477,7 +1477,7 @@
         <v>8</v>
       </c>
       <c r="B48" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -1488,10 +1488,10 @@
         <v>1</v>
       </c>
       <c r="E48" t="n">
-        <v>96</v>
+        <v>77</v>
       </c>
       <c r="F48" t="n">
-        <v>21</v>
+        <v>15</v>
       </c>
     </row>
     <row r="49">
@@ -1499,7 +1499,7 @@
         <v>9</v>
       </c>
       <c r="B49" t="n">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -1510,7 +1510,7 @@
         <v>1</v>
       </c>
       <c r="E49" t="n">
-        <v>254</v>
+        <v>114</v>
       </c>
       <c r="F49" t="n">
         <v>17</v>
@@ -1518,10 +1518,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B50" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -1532,18 +1532,18 @@
         <v>1</v>
       </c>
       <c r="E50" t="n">
-        <v>309</v>
+        <v>106</v>
       </c>
       <c r="F50" t="n">
-        <v>17</v>
+        <v>27</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="B51" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -1554,18 +1554,18 @@
         <v>1</v>
       </c>
       <c r="E51" t="n">
-        <v>116</v>
+        <v>98</v>
       </c>
       <c r="F51" t="n">
-        <v>21</v>
+        <v>17</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B52" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -1576,18 +1576,18 @@
         <v>1</v>
       </c>
       <c r="E52" t="n">
-        <v>133</v>
+        <v>127</v>
       </c>
       <c r="F52" t="n">
-        <v>21</v>
+        <v>13</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B53" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -1606,10 +1606,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B54" t="n">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -1620,18 +1620,18 @@
         <v>1</v>
       </c>
       <c r="E54" t="n">
-        <v>159</v>
+        <v>111</v>
       </c>
       <c r="F54" t="n">
-        <v>30</v>
+        <v>15</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B55" t="n">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -1642,18 +1642,18 @@
         <v>1</v>
       </c>
       <c r="E55" t="n">
-        <v>127</v>
+        <v>96</v>
       </c>
       <c r="F55" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="B56" t="n">
-        <v>14</v>
+        <v>22</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -1664,19 +1664,19 @@
         <v>1</v>
       </c>
       <c r="E56" t="n">
-        <v>219</v>
+        <v>216</v>
       </c>
       <c r="F56" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
+        <v>12</v>
+      </c>
+      <c r="B57" t="n">
         <v>13</v>
       </c>
-      <c r="B57" t="n">
-        <v>16</v>
-      </c>
       <c r="C57" t="inlineStr">
         <is>
           <t>Wall</t>
@@ -1686,18 +1686,18 @@
         <v>1</v>
       </c>
       <c r="E57" t="n">
-        <v>130</v>
+        <v>146</v>
       </c>
       <c r="F57" t="n">
-        <v>26</v>
+        <v>17</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B58" t="n">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -1708,18 +1708,18 @@
         <v>1</v>
       </c>
       <c r="E58" t="n">
-        <v>96</v>
+        <v>175</v>
       </c>
       <c r="F58" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B59" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -1730,10 +1730,10 @@
         <v>1</v>
       </c>
       <c r="E59" t="n">
-        <v>56</v>
+        <v>72</v>
       </c>
       <c r="F59" t="n">
-        <v>28</v>
+        <v>26</v>
       </c>
     </row>
     <row r="60">
@@ -1741,7 +1741,7 @@
         <v>14</v>
       </c>
       <c r="B60" t="n">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -1752,40 +1752,40 @@
         <v>1</v>
       </c>
       <c r="E60" t="n">
-        <v>216</v>
+        <v>84</v>
       </c>
       <c r="F60" t="n">
-        <v>16</v>
+        <v>21</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B61" t="n">
+        <v>20</v>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>Wall</t>
+        </is>
+      </c>
+      <c r="D61" t="n">
+        <v>1</v>
+      </c>
+      <c r="E61" t="n">
+        <v>166</v>
+      </c>
+      <c r="F61" t="n">
         <v>18</v>
-      </c>
-      <c r="C61" t="inlineStr">
-        <is>
-          <t>Wall</t>
-        </is>
-      </c>
-      <c r="D61" t="n">
-        <v>1</v>
-      </c>
-      <c r="E61" t="n">
-        <v>127</v>
-      </c>
-      <c r="F61" t="n">
-        <v>17</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="B62" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -1796,18 +1796,18 @@
         <v>1</v>
       </c>
       <c r="E62" t="n">
-        <v>212</v>
+        <v>142</v>
       </c>
       <c r="F62" t="n">
-        <v>26</v>
+        <v>134</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="B63" t="n">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -1818,15 +1818,15 @@
         <v>1</v>
       </c>
       <c r="E63" t="n">
-        <v>77</v>
+        <v>149</v>
       </c>
       <c r="F63" t="n">
-        <v>13</v>
+        <v>17</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="B64" t="n">
         <v>19</v>
@@ -1840,15 +1840,15 @@
         <v>1</v>
       </c>
       <c r="E64" t="n">
-        <v>212</v>
+        <v>148</v>
       </c>
       <c r="F64" t="n">
-        <v>28</v>
+        <v>25</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="B65" t="n">
         <v>20</v>
@@ -1862,10 +1862,186 @@
         <v>1</v>
       </c>
       <c r="E65" t="n">
-        <v>77</v>
+        <v>21</v>
       </c>
       <c r="F65" t="n">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="n">
         <v>15</v>
+      </c>
+      <c r="B66" t="n">
+        <v>22</v>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>Wall</t>
+        </is>
+      </c>
+      <c r="D66" t="n">
+        <v>1</v>
+      </c>
+      <c r="E66" t="n">
+        <v>216</v>
+      </c>
+      <c r="F66" t="n">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="n">
+        <v>15</v>
+      </c>
+      <c r="B67" t="n">
+        <v>21</v>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>Wall</t>
+        </is>
+      </c>
+      <c r="D67" t="n">
+        <v>1</v>
+      </c>
+      <c r="E67" t="n">
+        <v>96</v>
+      </c>
+      <c r="F67" t="n">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="n">
+        <v>17</v>
+      </c>
+      <c r="B68" t="n">
+        <v>20</v>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>Wall</t>
+        </is>
+      </c>
+      <c r="D68" t="n">
+        <v>1</v>
+      </c>
+      <c r="E68" t="n">
+        <v>116</v>
+      </c>
+      <c r="F68" t="n">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="n">
+        <v>18</v>
+      </c>
+      <c r="B69" t="n">
+        <v>19</v>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>Wall</t>
+        </is>
+      </c>
+      <c r="D69" t="n">
+        <v>1</v>
+      </c>
+      <c r="E69" t="n">
+        <v>148</v>
+      </c>
+      <c r="F69" t="n">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="n">
+        <v>20</v>
+      </c>
+      <c r="B70" t="n">
+        <v>22</v>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>Wall</t>
+        </is>
+      </c>
+      <c r="D70" t="n">
+        <v>1</v>
+      </c>
+      <c r="E70" t="n">
+        <v>133</v>
+      </c>
+      <c r="F70" t="n">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="n">
+        <v>21</v>
+      </c>
+      <c r="B71" t="n">
+        <v>22</v>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>Wall</t>
+        </is>
+      </c>
+      <c r="D71" t="n">
+        <v>1</v>
+      </c>
+      <c r="E71" t="n">
+        <v>219</v>
+      </c>
+      <c r="F71" t="n">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="n">
+        <v>3</v>
+      </c>
+      <c r="B72" t="n">
+        <v>12</v>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>Opening</t>
+        </is>
+      </c>
+      <c r="D72" t="n">
+        <v>1</v>
+      </c>
+      <c r="E72" t="n">
+        <v>123</v>
+      </c>
+      <c r="F72" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="n">
+        <v>4</v>
+      </c>
+      <c r="B73" t="n">
+        <v>14</v>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>Opening</t>
+        </is>
+      </c>
+      <c r="D73" t="n">
+        <v>1</v>
+      </c>
+      <c r="E73" t="n">
+        <v>166</v>
+      </c>
+      <c r="F73" t="n">
+        <v>43</v>
       </c>
     </row>
   </sheetData>

--- a/output/topology_excel/8422.xlsx
+++ b/output/topology_excel/8422.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F73"/>
+  <dimension ref="A1:H73"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -451,12 +451,22 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>Length</t>
+          <t>Length_1</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>Width</t>
+          <t>Width_1</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>Length_2</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>Width_2</t>
         </is>
       </c>
     </row>
@@ -481,6 +491,8 @@
       <c r="F2" t="n">
         <v>25</v>
       </c>
+      <c r="G2" t="inlineStr"/>
+      <c r="H2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -503,6 +515,8 @@
       <c r="F3" t="n">
         <v>17</v>
       </c>
+      <c r="G3" t="inlineStr"/>
+      <c r="H3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -525,6 +539,8 @@
       <c r="F4" t="n">
         <v>17</v>
       </c>
+      <c r="G4" t="inlineStr"/>
+      <c r="H4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -547,6 +563,8 @@
       <c r="F5" t="n">
         <v>25</v>
       </c>
+      <c r="G5" t="inlineStr"/>
+      <c r="H5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -569,6 +587,8 @@
       <c r="F6" t="n">
         <v>16</v>
       </c>
+      <c r="G6" t="inlineStr"/>
+      <c r="H6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -591,6 +611,8 @@
       <c r="F7" t="n">
         <v>21</v>
       </c>
+      <c r="G7" t="inlineStr"/>
+      <c r="H7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -613,6 +635,8 @@
       <c r="F8" t="n">
         <v>17</v>
       </c>
+      <c r="G8" t="inlineStr"/>
+      <c r="H8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -635,6 +659,8 @@
       <c r="F9" t="n">
         <v>18</v>
       </c>
+      <c r="G9" t="inlineStr"/>
+      <c r="H9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -657,6 +683,8 @@
       <c r="F10" t="n">
         <v>17</v>
       </c>
+      <c r="G10" t="inlineStr"/>
+      <c r="H10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -679,6 +707,8 @@
       <c r="F11" t="n">
         <v>15</v>
       </c>
+      <c r="G11" t="inlineStr"/>
+      <c r="H11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -701,6 +731,8 @@
       <c r="F12" t="n">
         <v>21</v>
       </c>
+      <c r="G12" t="inlineStr"/>
+      <c r="H12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -723,6 +755,8 @@
       <c r="F13" t="n">
         <v>13</v>
       </c>
+      <c r="G13" t="inlineStr"/>
+      <c r="H13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -745,6 +779,8 @@
       <c r="F14" t="n">
         <v>17</v>
       </c>
+      <c r="G14" t="inlineStr"/>
+      <c r="H14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -767,6 +803,8 @@
       <c r="F15" t="n">
         <v>15</v>
       </c>
+      <c r="G15" t="inlineStr"/>
+      <c r="H15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -789,6 +827,8 @@
       <c r="F16" t="n">
         <v>13</v>
       </c>
+      <c r="G16" t="inlineStr"/>
+      <c r="H16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -811,6 +851,8 @@
       <c r="F17" t="n">
         <v>15</v>
       </c>
+      <c r="G17" t="inlineStr"/>
+      <c r="H17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -833,6 +875,8 @@
       <c r="F18" t="n">
         <v>16</v>
       </c>
+      <c r="G18" t="inlineStr"/>
+      <c r="H18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -855,6 +899,8 @@
       <c r="F19" t="n">
         <v>16</v>
       </c>
+      <c r="G19" t="inlineStr"/>
+      <c r="H19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -877,6 +923,8 @@
       <c r="F20" t="n">
         <v>17</v>
       </c>
+      <c r="G20" t="inlineStr"/>
+      <c r="H20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -899,6 +947,8 @@
       <c r="F21" t="n">
         <v>25</v>
       </c>
+      <c r="G21" t="inlineStr"/>
+      <c r="H21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -921,6 +971,8 @@
       <c r="F22" t="n">
         <v>16</v>
       </c>
+      <c r="G22" t="inlineStr"/>
+      <c r="H22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -943,6 +995,8 @@
       <c r="F23" t="n">
         <v>25</v>
       </c>
+      <c r="G23" t="inlineStr"/>
+      <c r="H23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -965,6 +1019,8 @@
       <c r="F24" t="n">
         <v>25</v>
       </c>
+      <c r="G24" t="inlineStr"/>
+      <c r="H24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -987,6 +1043,8 @@
       <c r="F25" t="n">
         <v>16</v>
       </c>
+      <c r="G25" t="inlineStr"/>
+      <c r="H25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -1009,6 +1067,8 @@
       <c r="F26" t="n">
         <v>17</v>
       </c>
+      <c r="G26" t="inlineStr"/>
+      <c r="H26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -1023,13 +1083,19 @@
         </is>
       </c>
       <c r="D27" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E27" t="n">
-        <v>253</v>
+        <v>129</v>
       </c>
       <c r="F27" t="n">
-        <v>146</v>
+        <v>17</v>
+      </c>
+      <c r="G27" t="n">
+        <v>236</v>
+      </c>
+      <c r="H27" t="n">
+        <v>17</v>
       </c>
     </row>
     <row r="28">
@@ -1053,6 +1119,8 @@
       <c r="F28" t="n">
         <v>17</v>
       </c>
+      <c r="G28" t="inlineStr"/>
+      <c r="H28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -1075,6 +1143,8 @@
       <c r="F29" t="n">
         <v>27</v>
       </c>
+      <c r="G29" t="inlineStr"/>
+      <c r="H29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -1097,6 +1167,8 @@
       <c r="F30" t="n">
         <v>27</v>
       </c>
+      <c r="G30" t="inlineStr"/>
+      <c r="H30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -1119,6 +1191,8 @@
       <c r="F31" t="n">
         <v>17</v>
       </c>
+      <c r="G31" t="inlineStr"/>
+      <c r="H31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -1141,6 +1215,8 @@
       <c r="F32" t="n">
         <v>17</v>
       </c>
+      <c r="G32" t="inlineStr"/>
+      <c r="H32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -1163,6 +1239,8 @@
       <c r="F33" t="n">
         <v>17</v>
       </c>
+      <c r="G33" t="inlineStr"/>
+      <c r="H33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -1185,6 +1263,8 @@
       <c r="F34" t="n">
         <v>16</v>
       </c>
+      <c r="G34" t="inlineStr"/>
+      <c r="H34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -1207,6 +1287,8 @@
       <c r="F35" t="n">
         <v>16</v>
       </c>
+      <c r="G35" t="inlineStr"/>
+      <c r="H35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -1229,6 +1311,8 @@
       <c r="F36" t="n">
         <v>13</v>
       </c>
+      <c r="G36" t="inlineStr"/>
+      <c r="H36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -1251,6 +1335,8 @@
       <c r="F37" t="n">
         <v>17</v>
       </c>
+      <c r="G37" t="inlineStr"/>
+      <c r="H37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -1273,6 +1359,8 @@
       <c r="F38" t="n">
         <v>17</v>
       </c>
+      <c r="G38" t="inlineStr"/>
+      <c r="H38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -1295,6 +1383,8 @@
       <c r="F39" t="n">
         <v>26</v>
       </c>
+      <c r="G39" t="inlineStr"/>
+      <c r="H39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -1317,6 +1407,8 @@
       <c r="F40" t="n">
         <v>26</v>
       </c>
+      <c r="G40" t="inlineStr"/>
+      <c r="H40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -1339,6 +1431,8 @@
       <c r="F41" t="n">
         <v>13</v>
       </c>
+      <c r="G41" t="inlineStr"/>
+      <c r="H41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -1361,6 +1455,8 @@
       <c r="F42" t="n">
         <v>13</v>
       </c>
+      <c r="G42" t="inlineStr"/>
+      <c r="H42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -1383,6 +1479,8 @@
       <c r="F43" t="n">
         <v>30</v>
       </c>
+      <c r="G43" t="inlineStr"/>
+      <c r="H43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -1405,6 +1503,8 @@
       <c r="F44" t="n">
         <v>28</v>
       </c>
+      <c r="G44" t="inlineStr"/>
+      <c r="H44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -1427,6 +1527,8 @@
       <c r="F45" t="n">
         <v>17</v>
       </c>
+      <c r="G45" t="inlineStr"/>
+      <c r="H45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -1449,6 +1551,8 @@
       <c r="F46" t="n">
         <v>15</v>
       </c>
+      <c r="G46" t="inlineStr"/>
+      <c r="H46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -1471,6 +1575,8 @@
       <c r="F47" t="n">
         <v>28</v>
       </c>
+      <c r="G47" t="inlineStr"/>
+      <c r="H47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -1493,6 +1599,8 @@
       <c r="F48" t="n">
         <v>15</v>
       </c>
+      <c r="G48" t="inlineStr"/>
+      <c r="H48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -1515,6 +1623,8 @@
       <c r="F49" t="n">
         <v>17</v>
       </c>
+      <c r="G49" t="inlineStr"/>
+      <c r="H49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -1537,6 +1647,8 @@
       <c r="F50" t="n">
         <v>27</v>
       </c>
+      <c r="G50" t="inlineStr"/>
+      <c r="H50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -1559,6 +1671,8 @@
       <c r="F51" t="n">
         <v>17</v>
       </c>
+      <c r="G51" t="inlineStr"/>
+      <c r="H51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="n">
@@ -1581,6 +1695,8 @@
       <c r="F52" t="n">
         <v>13</v>
       </c>
+      <c r="G52" t="inlineStr"/>
+      <c r="H52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="n">
@@ -1603,6 +1719,8 @@
       <c r="F53" t="n">
         <v>21</v>
       </c>
+      <c r="G53" t="inlineStr"/>
+      <c r="H53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="n">
@@ -1625,6 +1743,8 @@
       <c r="F54" t="n">
         <v>15</v>
       </c>
+      <c r="G54" t="inlineStr"/>
+      <c r="H54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="n">
@@ -1647,6 +1767,8 @@
       <c r="F55" t="n">
         <v>16</v>
       </c>
+      <c r="G55" t="inlineStr"/>
+      <c r="H55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="n">
@@ -1669,6 +1791,8 @@
       <c r="F56" t="n">
         <v>16</v>
       </c>
+      <c r="G56" t="inlineStr"/>
+      <c r="H56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="n">
@@ -1691,6 +1815,8 @@
       <c r="F57" t="n">
         <v>17</v>
       </c>
+      <c r="G57" t="inlineStr"/>
+      <c r="H57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="n">
@@ -1713,6 +1839,8 @@
       <c r="F58" t="n">
         <v>17</v>
       </c>
+      <c r="G58" t="inlineStr"/>
+      <c r="H58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="n">
@@ -1735,6 +1863,8 @@
       <c r="F59" t="n">
         <v>26</v>
       </c>
+      <c r="G59" t="inlineStr"/>
+      <c r="H59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="n">
@@ -1757,6 +1887,8 @@
       <c r="F60" t="n">
         <v>21</v>
       </c>
+      <c r="G60" t="inlineStr"/>
+      <c r="H60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="n">
@@ -1779,6 +1911,8 @@
       <c r="F61" t="n">
         <v>18</v>
       </c>
+      <c r="G61" t="inlineStr"/>
+      <c r="H61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="n">
@@ -1793,13 +1927,19 @@
         </is>
       </c>
       <c r="D62" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E62" t="n">
-        <v>142</v>
+        <v>127</v>
       </c>
       <c r="F62" t="n">
-        <v>134</v>
+        <v>18</v>
+      </c>
+      <c r="G62" t="n">
+        <v>116</v>
+      </c>
+      <c r="H62" t="n">
+        <v>15</v>
       </c>
     </row>
     <row r="63">
@@ -1823,6 +1963,8 @@
       <c r="F63" t="n">
         <v>17</v>
       </c>
+      <c r="G63" t="inlineStr"/>
+      <c r="H63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="n">
@@ -1845,6 +1987,8 @@
       <c r="F64" t="n">
         <v>25</v>
       </c>
+      <c r="G64" t="inlineStr"/>
+      <c r="H64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="n">
@@ -1867,6 +2011,8 @@
       <c r="F65" t="n">
         <v>21</v>
       </c>
+      <c r="G65" t="inlineStr"/>
+      <c r="H65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="n">
@@ -1887,8 +2033,10 @@
         <v>216</v>
       </c>
       <c r="F66" t="n">
-        <v>73</v>
-      </c>
+        <v>46</v>
+      </c>
+      <c r="G66" t="inlineStr"/>
+      <c r="H66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="n">
@@ -1911,6 +2059,8 @@
       <c r="F67" t="n">
         <v>21</v>
       </c>
+      <c r="G67" t="inlineStr"/>
+      <c r="H67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="n">
@@ -1933,6 +2083,8 @@
       <c r="F68" t="n">
         <v>21</v>
       </c>
+      <c r="G68" t="inlineStr"/>
+      <c r="H68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="n">
@@ -1955,6 +2107,8 @@
       <c r="F69" t="n">
         <v>17</v>
       </c>
+      <c r="G69" t="inlineStr"/>
+      <c r="H69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="n">
@@ -1977,6 +2131,8 @@
       <c r="F70" t="n">
         <v>21</v>
       </c>
+      <c r="G70" t="inlineStr"/>
+      <c r="H70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="n">
@@ -1999,6 +2155,8 @@
       <c r="F71" t="n">
         <v>18</v>
       </c>
+      <c r="G71" t="inlineStr"/>
+      <c r="H71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="n">
@@ -2021,6 +2179,8 @@
       <c r="F72" t="n">
         <v>1</v>
       </c>
+      <c r="G72" t="inlineStr"/>
+      <c r="H72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="n">
@@ -2043,6 +2203,8 @@
       <c r="F73" t="n">
         <v>43</v>
       </c>
+      <c r="G73" t="inlineStr"/>
+      <c r="H73" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
